--- a/results/job_matches_2026-07-17.xlsx
+++ b/results/job_matches_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:G187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,77 +538,77 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.9</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, S3, RDS, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, clustering keys</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b22cbf19f8a0047</t>
+          <t>https://www.indeed.com/viewjob?jk=ba13c042faeff40f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22.2</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, clustering keys</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba13c042faeff40f</t>
+          <t>https://www.indeed.com/viewjob?jk=12d58810cbcb954b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -631,37 +631,37 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12d58810cbcb954b</t>
+          <t>https://www.indeed.com/viewjob?jk=c01844276a565bcb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Engineer - iOS/Android</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01844276a565bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=ea7bf7c8fec07038</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea7bf7c8fec07038</t>
+          <t>https://www.indeed.com/viewjob?jk=d004a662bac9f5e2</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004a662bac9f5e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c7aaa1ab54a6fb47</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7aaa1ab54a6fb47</t>
+          <t>https://www.indeed.com/viewjob?jk=bdde81364ace6b88</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer - iOS/Android</t>
+          <t>AWS Platform Specialist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdde81364ace6b88</t>
+          <t>https://www.indeed.com/viewjob?jk=30dc1ebf3576193b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Platform Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Excel Sports Management</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, Azure, GCP, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30dc1ebf3576193b</t>
+          <t>https://www.indeed.com/viewjob?jk=54c48dbd46696795</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Excel Sports Management</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, Azure, GCP, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Vertex AI, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c48dbd46696795</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3a80ab86734aea</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Reliability Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Vertex AI, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, Tableau, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3a80ab86734aea</t>
+          <t>https://www.indeed.com/viewjob?jk=3b0948bec3ed1512</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba9a5d942e523c5</t>
+          <t>https://www.indeed.com/viewjob?jk=bd9b93bfe4203dee</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd9b93bfe4203dee</t>
+          <t>https://www.indeed.com/viewjob?jk=3eda973817d320c4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eda973817d320c4</t>
+          <t>https://www.indeed.com/viewjob?jk=9409951346a7ad0d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Hadoop/Spark/OCP/Big Data</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa14baaf9fd7957</t>
+          <t>https://www.indeed.com/viewjob?jk=af009d50d9ce471a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeade119569bbf7</t>
+          <t>https://www.indeed.com/viewjob?jk=b475180d99aecacf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93edda5c98f4cdb4</t>
+          <t>https://www.indeed.com/viewjob?jk=772d08b80e754e75</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1cdcb324b377bf</t>
+          <t>https://www.indeed.com/viewjob?jk=e3fd193c06ae0581</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bc1107dcef567b</t>
+          <t>https://www.indeed.com/viewjob?jk=2b65c34e565b992c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab6ea52221dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=0779fe138ded484b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b1bb8e723d49656</t>
+          <t>https://www.indeed.com/viewjob?jk=cb1c755d148975ff</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
+          <t>https://www.indeed.com/viewjob?jk=613cd064c5c54a4c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Power BI Data Architect</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Essent Guaranty, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b04eecb0db1a644</t>
+          <t>https://www.indeed.com/viewjob?jk=120779d15d1fcfb6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c7b5c770c1535f</t>
+          <t>https://www.indeed.com/viewjob?jk=67914dd58a58a8d4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf29b9a8949927c0</t>
+          <t>https://www.indeed.com/viewjob?jk=a31d4f4143f7cb28</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e9ac43a4c79de0</t>
+          <t>https://www.indeed.com/viewjob?jk=4a5289604bca0cff</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Azure Data Engineer – AI &amp; Data Platform</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ea6d5281a59460</t>
+          <t>https://www.indeed.com/viewjob?jk=f3fe4280a2c93391</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6f565a0cba9b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=cae284e6548c3258</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93a6382b79298c2</t>
+          <t>https://www.indeed.com/viewjob?jk=fbe9517a3231d13b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c55cbc7a32077d</t>
+          <t>https://www.indeed.com/viewjob?jk=425185029b9803cd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bfd9be8468f66b3</t>
+          <t>https://www.indeed.com/viewjob?jk=05e4cfd7cccd7103</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f547f3d8df9f9bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=ee699af0925dbbc0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54854fd47b363a4</t>
+          <t>https://www.indeed.com/viewjob?jk=beebec88652a0ad1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45df0d1609c8367b</t>
+          <t>https://www.indeed.com/viewjob?jk=d241129f70a15de3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23bdc76018751755</t>
+          <t>https://www.indeed.com/viewjob?jk=811f9831e5bf2622</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43290df41714a389</t>
+          <t>https://www.indeed.com/viewjob?jk=48d5324a2b8a1805</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b16b2331ee1aa84</t>
+          <t>https://www.indeed.com/viewjob?jk=50f7ae8262615bc7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b04e833dd19df0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=13b295f641478562</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259cc44945602b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7c092bdfadcd07b8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4feede92620f22e9</t>
+          <t>https://www.indeed.com/viewjob?jk=e4028439241ee86b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbebd14ac0ed49c4</t>
+          <t>https://www.indeed.com/viewjob?jk=f7c190952f3113a4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e43910adecb4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d90ab183a51383</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2756336b0144995b</t>
+          <t>https://www.indeed.com/viewjob?jk=c10752c112f86257</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41c68f32e47611a1</t>
+          <t>https://www.indeed.com/viewjob?jk=523d0e5286ecdc4d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd8d2e3100ea907</t>
+          <t>https://www.indeed.com/viewjob?jk=40492208ab43d208</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e69471258c9ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cd193841933bb</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer - Hadoop/Spark/OCP/Big Data</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba35650e2da9649</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa14baaf9fd7957</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb9c24b4a27b99e</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeade119569bbf7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08abb8a8067dabe</t>
+          <t>https://www.indeed.com/viewjob?jk=93edda5c98f4cdb4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5c390fe780fb83</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1cdcb324b377bf</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10e7c9ecd47ff09</t>
+          <t>https://www.indeed.com/viewjob?jk=06bc1107dcef567b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9393aab76aef47</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab6ea52221dfe</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de5598243142a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b1bb8e723d49656</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4f92e0b5a77250</t>
+          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b5097fd06a5b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f1eb8e2a6e504b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dbcec9a2251bc8e</t>
+          <t>https://www.indeed.com/viewjob?jk=587249eddf698e94</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1abb06a257adfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c7b5c770c1535f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ccd80ac908db0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=bf29b9a8949927c0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09da3c6a02110e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e9ac43a4c79de0</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b81878d33b2cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6f565a0cba9b6c</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2fc82662d2d577e</t>
+          <t>https://www.indeed.com/viewjob?jk=a93a6382b79298c2</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f11a2204aeac9</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c55cbc7a32077d</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4bd4f9915f719</t>
+          <t>https://www.indeed.com/viewjob?jk=2bfd9be8468f66b3</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d99d8a28b97414</t>
+          <t>https://www.indeed.com/viewjob?jk=f547f3d8df9f9bcc</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e41db969f64f04</t>
+          <t>https://www.indeed.com/viewjob?jk=d54854fd47b363a4</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e92b6c49d12909</t>
+          <t>https://www.indeed.com/viewjob?jk=45df0d1609c8367b</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad5fe900bb21047</t>
+          <t>https://www.indeed.com/viewjob?jk=23bdc76018751755</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6e55b5d347e590</t>
+          <t>https://www.indeed.com/viewjob?jk=43290df41714a389</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4055b440fbf4926</t>
+          <t>https://www.indeed.com/viewjob?jk=2b16b2331ee1aa84</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d661b2249c160667</t>
+          <t>https://www.indeed.com/viewjob?jk=b04e833dd19df0f2</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7fb86315501bea</t>
+          <t>https://www.indeed.com/viewjob?jk=9259cc44945602b4</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48351a9424c5adaf</t>
+          <t>https://www.indeed.com/viewjob?jk=4feede92620f22e9</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=449ffea81d7dabee</t>
+          <t>https://www.indeed.com/viewjob?jk=bbebd14ac0ed49c4</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b4c29a1cbe80d1</t>
+          <t>https://www.indeed.com/viewjob?jk=14e43910adecb4e3</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed68905fe7cf4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=2756336b0144995b</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0cd86430f84239c</t>
+          <t>https://www.indeed.com/viewjob?jk=41c68f32e47611a1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd8d2e3100ea907</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=15e69471258c9ba0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba35650e2da9649</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Enginnering</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
+          <t>https://www.indeed.com/viewjob?jk=afb9c24b4a27b99e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Managing Solution Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2640726ebc83e1eb</t>
+          <t>https://www.indeed.com/viewjob?jk=c08abb8a8067dabe</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Managing Solution Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99663228cfbf0951</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5c390fe780fb83</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (East Coast)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=e10e7c9ecd47ff09</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>OIC Platform Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9393aab76aef47</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Build-A-Bear Workshop</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
+          <t>https://www.indeed.com/viewjob?jk=2de5598243142a0c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Reno, NV, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4f92e0b5a77250</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>STORD Warehouse</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Glue, IAM, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
+          <t>https://www.indeed.com/viewjob?jk=33b5097fd06a5b1c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Technical Solutions Engineer - Pre</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Verily</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,137 +3611,137 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
+          <t>https://www.indeed.com/viewjob?jk=2dbcec9a2251bc8e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Batchelor &amp; Kimball</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Conyers, GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=f1abb06a257adfd5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=3ccd80ac908db0d1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
+          <t>https://www.indeed.com/viewjob?jk=c09da3c6a02110e7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Devops Engineer (remote)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b81878d33b2cc7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DevOps Engineer (local)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
+          <t>https://www.indeed.com/viewjob?jk=b2fc82662d2d577e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Real-Time Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=143f11a2204aeac9</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4bd4f9915f719</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hopkinton, MA, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
+          <t>https://www.indeed.com/viewjob?jk=94d99d8a28b97414</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e41db969f64f04</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MicroStrategy Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Data Meaning</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e92b6c49d12909</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Lambda, Scala, Kafka, Oracle, MySQL, MongoDB, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1b6ba41a8a56f2</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad5fe900bb21047</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Lambda, Scala, Kafka, Oracle, MySQL, MongoDB, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d95cae4e2d404f</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6e55b5d347e590</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Lambda, Scala, Kafka, Oracle, MySQL, MongoDB, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c221ea0da8a688bf</t>
+          <t>https://www.indeed.com/viewjob?jk=b4055b440fbf4926</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer (Global)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
+          <t>https://www.indeed.com/viewjob?jk=d661b2249c160667</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer II - Big Data &amp; AWS</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7fb86315501bea</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
+          <t>https://www.indeed.com/viewjob?jk=48351a9424c5adaf</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
+          <t>https://www.indeed.com/viewjob?jk=449ffea81d7dabee</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
+          <t>https://www.indeed.com/viewjob?jk=92b4c29a1cbe80d1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed68905fe7cf4c8</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a0cd86430f84239c</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,67 +4381,67 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
+          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
+          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Senior Solutions Architect - Airflow (East Coast)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Philadelphia, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
+          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect (Remote)</t>
+          <t>Senior Software Enginnering</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
+          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Engineer, Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b05fe1f7203164</t>
+          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>QA Automation Engineer - Brokerage/ Financial domain</t>
+          <t>OIC Platform Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Inabia Software &amp; Consulting Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e248d1d788eee10</t>
+          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Junior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Clarity Innovations, LLC</t>
+          <t>Build-A-Bear Workshop</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Universal City, CA, US USA</t>
+          <t>Reno, NV, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6537fbdf744212f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>STORD Warehouse</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>Glue, IAM, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
+          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Technical Solutions Engineer - Pre</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Wellvana Health</t>
+          <t>Verily</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,67 +4731,67 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Platform Foundation</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
+          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
+          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
+          <t>Devops Engineer (remote)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,67 +4836,67 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
+          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer (local)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Informatica Intelligent Data Management Cloud</t>
+          <t>Real-Time Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14760973f99a8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,102 +4941,102 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
+          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hopkinton, MA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba2d09365f6ee5a</t>
+          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Software Engineering, Sr Engineer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
+          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
+          <t>MicroStrategy Architect</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Data Meaning</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
+          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>JSSA</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>Lambda, Scala, Kafka, Oracle, MySQL, MongoDB, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
+          <t>https://www.indeed.com/viewjob?jk=af1b6ba41a8a56f2</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Specialist, Application Development</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
+          <t>Lambda, Scala, Kafka, Oracle, MySQL, MongoDB, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d95cae4e2d404f</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>IT Data Scientist</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>Lambda, Scala, Kafka, Oracle, MySQL, MongoDB, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac351039409cb17</t>
+          <t>https://www.indeed.com/viewjob?jk=c221ea0da8a688bf</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Engineer II, Advanced Research (Remote)</t>
+          <t>AI DevOps Engineer (Global)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,32 +5186,32 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e40cb2a69d120f5</t>
+          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (API-focused)</t>
+          <t>Software Engineer II - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Off Duty Management</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Katy, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,32 +5221,32 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>COE QE DevOps role - C1</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,32 +5256,32 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
+          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Project Controls, Database Administrator (DBA)</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,32 +5291,32 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f66e61d041240a</t>
+          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Project Controls, Database Administrator (DBA)</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,32 +5326,32 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df8062c19c4d1d41</t>
+          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,32 +5361,32 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
+          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,32 +5396,32 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
+          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Software Engineer II - SRE</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,32 +5431,32 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
+          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,32 +5466,32 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
+          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,32 +5501,32 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
+          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Grafana Engineer</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,32 +5536,32 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Grafana Engineer</t>
+          <t>Cloud Solution Architect (Remote)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,67 +5571,67 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
+          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Red Hat OpenShift Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b05fe1f7203164</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Architect</t>
+          <t>QA Automation Engineer - Brokerage/ Financial domain</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Softpath System LLC</t>
+          <t>Inabia Software &amp; Consulting Inc.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,32 +5641,32 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64c763f434149f33</t>
+          <t>https://www.indeed.com/viewjob?jk=7e248d1d788eee10</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Junior Platform Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Enterprise Knowledge</t>
+          <t>Clarity Innovations, LLC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,32 +5676,32 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
+          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Workday Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>College Board</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Universal City, CA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,32 +5711,32 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a180802b9be9366</t>
+          <t>https://www.indeed.com/viewjob?jk=6537fbdf744212f8</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Sr. System Administrator</t>
+          <t>Senior Java Engineer with NetSuite Experience</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,75 +5746,1230 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61836c41197600ef</t>
+          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Dynamo Technologies</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Aberdeen Proving Ground, MD, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=522e7d02e7987862</t>
+          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Wellvana Health</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer – Platform Foundation</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Informatica Intelligent Data Management Cloud</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Schaumburg, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b14760973f99a8d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Synopsys</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ba2d09365f6ee5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Senior Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Kafka, SQL Server, Data Modeling, Splunk, CI/CD, Jenkins, Maven, Docker</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d97138d9df18fcba</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>MiniMed</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Northridge, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>JSSA</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Rockville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Senior Specialist, Application Development</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>BNY</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>IT Data Scientist</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>AdventHealth Corporate</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Altamonte Springs, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ac351039409cb17</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Engineer II, Advanced Research (Remote)</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e40cb2a69d120f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Backend Software Engineer (API-focused)</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Off Duty Management</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Katy, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>COE QE DevOps role - C1</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Simpson Strong-Tie</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Software Engineering, Sr Engineer</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Synopsys</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Santa Fe, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Project Controls, Database Administrator (DBA)</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5f66e61d041240a</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Project Controls, Database Administrator (DBA)</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Columbia, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df8062c19c4d1d41</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Merck KGaA</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Pacific Life</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>BNY</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Software Engineer II - SRE</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Township of Hamilton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Defense Unicorns</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Defense Unicorns</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Senior Grafana Engineer</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Senior Grafana Engineer</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Red Hat OpenShift Engineer</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa01236e58a71dfc</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Java Architect</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Softpath System LLC</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Newark, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64c763f434149f33</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Senior Workday Engineer</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>College Board</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a180802b9be9366</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Dynamo Technologies</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Aberdeen Proving Ground, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=522e7d02e7987862</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
           <t>Senior Tableau &amp; Alteryx Administrator (Cloud + DevOps Expertise)</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B187" t="inlineStr">
         <is>
           <t>Intone Networks</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
+      <c r="C187" t="inlineStr">
         <is>
           <t>Winterville, NC, US USA</t>
         </is>
       </c>
-      <c r="D154" t="n">
+      <c r="D187" t="n">
         <v>10.4</v>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="E187" t="inlineStr">
         <is>
           <t>AWS, Lambda, Redshift, Step Functions, RDS, Kafka, Tableau, Tableau Server, CI/CD, Terraform</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=653b8eca70818820</t>
         </is>

--- a/results/job_matches_2026-07-17.xlsx
+++ b/results/job_matches_2026-07-17.xlsx
@@ -573,7 +573,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,19 +596,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12d58810cbcb954b</t>
+          <t>https://www.indeed.com/viewjob?jk=387fc6b51ae76f3d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -631,177 +631,177 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01844276a565bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=12d58810cbcb954b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer - iOS/Android</t>
+          <t>AWS Platform Specialist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea7bf7c8fec07038</t>
+          <t>https://www.indeed.com/viewjob?jk=30dc1ebf3576193b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer - iOS/Android</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Excel Sports Management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, Azure, GCP, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004a662bac9f5e2</t>
+          <t>https://www.indeed.com/viewjob?jk=54c48dbd46696795</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer - iOS/Android</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Vertex AI, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7aaa1ab54a6fb47</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3a80ab86734aea</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer - iOS/Android</t>
+          <t>Reliability Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, Tableau, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdde81364ace6b88</t>
+          <t>https://www.indeed.com/viewjob?jk=3b0948bec3ed1512</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AWS Platform Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30dc1ebf3576193b</t>
+          <t>https://www.indeed.com/viewjob?jk=bd9b93bfe4203dee</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Excel Sports Management</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, Azure, GCP, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c48dbd46696795</t>
+          <t>https://www.indeed.com/viewjob?jk=3eda973817d320c4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Vertex AI, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3a80ab86734aea</t>
+          <t>https://www.indeed.com/viewjob?jk=9409951346a7ad0d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Reliability Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, Tableau, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b0948bec3ed1512</t>
+          <t>https://www.indeed.com/viewjob?jk=af009d50d9ce471a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd9b93bfe4203dee</t>
+          <t>https://www.indeed.com/viewjob?jk=b475180d99aecacf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eda973817d320c4</t>
+          <t>https://www.indeed.com/viewjob?jk=772d08b80e754e75</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9409951346a7ad0d</t>
+          <t>https://www.indeed.com/viewjob?jk=e3fd193c06ae0581</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af009d50d9ce471a</t>
+          <t>https://www.indeed.com/viewjob?jk=2b65c34e565b992c</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b475180d99aecacf</t>
+          <t>https://www.indeed.com/viewjob?jk=0779fe138ded484b</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772d08b80e754e75</t>
+          <t>https://www.indeed.com/viewjob?jk=cb1c755d148975ff</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3fd193c06ae0581</t>
+          <t>https://www.indeed.com/viewjob?jk=613cd064c5c54a4c</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b65c34e565b992c</t>
+          <t>https://www.indeed.com/viewjob?jk=120779d15d1fcfb6</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779fe138ded484b</t>
+          <t>https://www.indeed.com/viewjob?jk=67914dd58a58a8d4</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb1c755d148975ff</t>
+          <t>https://www.indeed.com/viewjob?jk=a31d4f4143f7cb28</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613cd064c5c54a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a5289604bca0cff</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=120779d15d1fcfb6</t>
+          <t>https://www.indeed.com/viewjob?jk=f3fe4280a2c93391</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67914dd58a58a8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=cae284e6548c3258</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31d4f4143f7cb28</t>
+          <t>https://www.indeed.com/viewjob?jk=fbe9517a3231d13b</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a5289604bca0cff</t>
+          <t>https://www.indeed.com/viewjob?jk=425185029b9803cd</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3fe4280a2c93391</t>
+          <t>https://www.indeed.com/viewjob?jk=05e4cfd7cccd7103</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae284e6548c3258</t>
+          <t>https://www.indeed.com/viewjob?jk=ee699af0925dbbc0</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbe9517a3231d13b</t>
+          <t>https://www.indeed.com/viewjob?jk=beebec88652a0ad1</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425185029b9803cd</t>
+          <t>https://www.indeed.com/viewjob?jk=d241129f70a15de3</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e4cfd7cccd7103</t>
+          <t>https://www.indeed.com/viewjob?jk=811f9831e5bf2622</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee699af0925dbbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=48d5324a2b8a1805</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beebec88652a0ad1</t>
+          <t>https://www.indeed.com/viewjob?jk=50f7ae8262615bc7</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d241129f70a15de3</t>
+          <t>https://www.indeed.com/viewjob?jk=13b295f641478562</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811f9831e5bf2622</t>
+          <t>https://www.indeed.com/viewjob?jk=7c092bdfadcd07b8</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d5324a2b8a1805</t>
+          <t>https://www.indeed.com/viewjob?jk=e4028439241ee86b</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50f7ae8262615bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=f7c190952f3113a4</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b295f641478562</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d90ab183a51383</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c092bdfadcd07b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c10752c112f86257</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4028439241ee86b</t>
+          <t>https://www.indeed.com/viewjob?jk=523d0e5286ecdc4d</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7c190952f3113a4</t>
+          <t>https://www.indeed.com/viewjob?jk=40492208ab43d208</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,19 +2001,19 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d90ab183a51383</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cd193841933bb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Senior Data Engineer - Hadoop/Spark/OCP/Big Data</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10752c112f86257</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa14baaf9fd7957</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523d0e5286ecdc4d</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeade119569bbf7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40492208ab43d208</t>
+          <t>https://www.indeed.com/viewjob?jk=93edda5c98f4cdb4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cd193841933bb</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1cdcb324b377bf</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Hadoop/Spark/OCP/Big Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa14baaf9fd7957</t>
+          <t>https://www.indeed.com/viewjob?jk=06bc1107dcef567b</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeade119569bbf7</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab6ea52221dfe</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93edda5c98f4cdb4</t>
+          <t>https://www.indeed.com/viewjob?jk=5b1bb8e723d49656</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MDM Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1cdcb324b377bf</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c2c9fdda4f8d1c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bc1107dcef567b</t>
+          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
         </is>
       </c>
     </row>
@@ -2328,20 +2328,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab6ea52221dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f1eb8e2a6e504b</t>
         </is>
       </c>
     </row>
@@ -2363,20 +2363,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b1bb8e723d49656</t>
+          <t>https://www.indeed.com/viewjob?jk=587249eddf698e94</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c7b5c770c1535f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f1eb8e2a6e504b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf29b9a8949927c0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587249eddf698e94</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e9ac43a4c79de0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c7b5c770c1535f</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6f565a0cba9b6c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf29b9a8949927c0</t>
+          <t>https://www.indeed.com/viewjob?jk=a93a6382b79298c2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e9ac43a4c79de0</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c55cbc7a32077d</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6f565a0cba9b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2bfd9be8468f66b3</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93a6382b79298c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f547f3d8df9f9bcc</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c55cbc7a32077d</t>
+          <t>https://www.indeed.com/viewjob?jk=d54854fd47b363a4</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bfd9be8468f66b3</t>
+          <t>https://www.indeed.com/viewjob?jk=45df0d1609c8367b</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f547f3d8df9f9bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=23bdc76018751755</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54854fd47b363a4</t>
+          <t>https://www.indeed.com/viewjob?jk=43290df41714a389</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45df0d1609c8367b</t>
+          <t>https://www.indeed.com/viewjob?jk=2b16b2331ee1aa84</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23bdc76018751755</t>
+          <t>https://www.indeed.com/viewjob?jk=b04e833dd19df0f2</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43290df41714a389</t>
+          <t>https://www.indeed.com/viewjob?jk=9259cc44945602b4</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b16b2331ee1aa84</t>
+          <t>https://www.indeed.com/viewjob?jk=4feede92620f22e9</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b04e833dd19df0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=bbebd14ac0ed49c4</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259cc44945602b4</t>
+          <t>https://www.indeed.com/viewjob?jk=14e43910adecb4e3</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4feede92620f22e9</t>
+          <t>https://www.indeed.com/viewjob?jk=2756336b0144995b</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbebd14ac0ed49c4</t>
+          <t>https://www.indeed.com/viewjob?jk=41c68f32e47611a1</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e43910adecb4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd8d2e3100ea907</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2756336b0144995b</t>
+          <t>https://www.indeed.com/viewjob?jk=15e69471258c9ba0</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41c68f32e47611a1</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba35650e2da9649</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd8d2e3100ea907</t>
+          <t>https://www.indeed.com/viewjob?jk=afb9c24b4a27b99e</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e69471258c9ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=c08abb8a8067dabe</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba35650e2da9649</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5c390fe780fb83</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb9c24b4a27b99e</t>
+          <t>https://www.indeed.com/viewjob?jk=e10e7c9ecd47ff09</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08abb8a8067dabe</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9393aab76aef47</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5c390fe780fb83</t>
+          <t>https://www.indeed.com/viewjob?jk=2de5598243142a0c</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10e7c9ecd47ff09</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4f92e0b5a77250</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9393aab76aef47</t>
+          <t>https://www.indeed.com/viewjob?jk=33b5097fd06a5b1c</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de5598243142a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=2dbcec9a2251bc8e</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4f92e0b5a77250</t>
+          <t>https://www.indeed.com/viewjob?jk=f1abb06a257adfd5</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b5097fd06a5b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=3ccd80ac908db0d1</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dbcec9a2251bc8e</t>
+          <t>https://www.indeed.com/viewjob?jk=c09da3c6a02110e7</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1abb06a257adfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b81878d33b2cc7</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ccd80ac908db0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=b2fc82662d2d577e</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09da3c6a02110e7</t>
+          <t>https://www.indeed.com/viewjob?jk=143f11a2204aeac9</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b81878d33b2cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4bd4f9915f719</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2fc82662d2d577e</t>
+          <t>https://www.indeed.com/viewjob?jk=94d99d8a28b97414</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f11a2204aeac9</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e41db969f64f04</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4bd4f9915f719</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e92b6c49d12909</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d99d8a28b97414</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad5fe900bb21047</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e41db969f64f04</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6e55b5d347e590</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e92b6c49d12909</t>
+          <t>https://www.indeed.com/viewjob?jk=b4055b440fbf4926</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad5fe900bb21047</t>
+          <t>https://www.indeed.com/viewjob?jk=d661b2249c160667</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6e55b5d347e590</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7fb86315501bea</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4055b440fbf4926</t>
+          <t>https://www.indeed.com/viewjob?jk=48351a9424c5adaf</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d661b2249c160667</t>
+          <t>https://www.indeed.com/viewjob?jk=449ffea81d7dabee</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7fb86315501bea</t>
+          <t>https://www.indeed.com/viewjob?jk=92b4c29a1cbe80d1</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48351a9424c5adaf</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed68905fe7cf4c8</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=449ffea81d7dabee</t>
+          <t>https://www.indeed.com/viewjob?jk=a0cd86430f84239c</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b4c29a1cbe80d1</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed68905fe7cf4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0cd86430f84239c</t>
+          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Solutions Architect - Airflow (East Coast)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Senior Software Enginnering</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,54 +4416,54 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
+          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (East Coast)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Oracle Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4472,46 +4472,46 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
+          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Enginnering</t>
+          <t>Data Engineer, Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
+          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer, Forward Deployed Engineer</t>
+          <t>OIC Platform Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
+          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>OIC Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Build-A-Bear Workshop</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Build-A-Bear Workshop</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Reno, NV, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>STORD Warehouse</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Reno, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>Glue, IAM, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
+          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Technical Solutions Engineer - Pre</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>STORD Warehouse</t>
+          <t>Verily</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Glue, IAM, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Technical Solutions Engineer - Pre</t>
+          <t>Analytics Platform Engineer Alteryx</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Verily</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Garland, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
+          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Devops Engineer (remote)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,14 +4801,14 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
+          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Devops Engineer (remote)</t>
+          <t>DevOps Engineer (local)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
+          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DevOps Engineer (local)</t>
+          <t>Real-Time Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
+          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Real-Time Data Engineer</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hopkinton, MA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Apache Kafka Developer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Hopkinton, MA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,14 +4976,14 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
+          <t>https://www.indeed.com/viewjob?jk=60ffb92f7d3b11c8</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Apache Kafka Developer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,19 +5011,19 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MicroStrategy Architect</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Data Meaning</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
+          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>MicroStrategy Architect</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Data Meaning</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Lambda, Scala, Kafka, Oracle, MySQL, MongoDB, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1b6ba41a8a56f2</t>
+          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d95cae4e2d404f</t>
+          <t>https://www.indeed.com/viewjob?jk=af1b6ba41a8a56f2</t>
         </is>
       </c>
     </row>
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c221ea0da8a688bf</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d95cae4e2d404f</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer (Global)</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>Lambda, Scala, Kafka, Oracle, MySQL, MongoDB, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,32 +5186,32 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c221ea0da8a688bf</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Software Engineer II - Big Data &amp; AWS</t>
+          <t>AI DevOps Engineer (Global)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
+          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Software Engineer II - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
+          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
+          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
+          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
+          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
+          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
+          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
+          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
+          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect (Remote)</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
+          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Cloud Solution Architect (Remote)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b05fe1f7203164</t>
+          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
         </is>
       </c>
     </row>
@@ -6103,17 +6103,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Engineer II, Advanced Research (Remote)</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JSSA</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
+          <t>https://www.indeed.com/viewjob?jk=8e40cb2a69d120f5</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Senior Specialist, Application Development</t>
+          <t>Backend Software Engineer (API-focused)</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Off Duty Management</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Katy, TX, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>IT Data Scientist</t>
+          <t>COE QE DevOps role - C1</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac351039409cb17</t>
+          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Engineer II, Advanced Research (Remote)</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>JSSA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e40cb2a69d120f5</t>
+          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (API-focused)</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Off Duty Management</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Katy, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>COE QE DevOps role - C1</t>
+          <t>Software Engineering, Sr Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,34 +6296,34 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
+          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Senior Specialist, Application Development</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
+          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Software Engineering, Sr Engineer</t>
+          <t>IT Data Scientist</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,17 +6366,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac351039409cb17</t>
         </is>
       </c>
     </row>
@@ -6453,17 +6453,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Database Developer Expert</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Merck KGaA</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
+          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Merck KGaA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6516,24 +6516,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Software Engineer II - SRE</t>
+          <t>OpenShift Administrator</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,29 +6576,29 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II - SRE</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
+          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Senior Grafana Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Senior Grafana Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Red Hat OpenShift Engineer</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,34 +6751,34 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
+          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa01236e58a71dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Architect</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Softpath System LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,24 +6831,24 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64c763f434149f33</t>
+          <t>https://www.indeed.com/viewjob?jk=aa01236e58a71dfc</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Senior Full Stack Java Architect</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Enterprise Knowledge</t>
+          <t>Softpath System LLC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
+          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,24 +6866,24 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
+          <t>https://www.indeed.com/viewjob?jk=64c763f434149f33</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Senior Workday Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>College Board</t>
+          <t>Enterprise Knowledge</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a180802b9be9366</t>
+          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-17.xlsx
+++ b/results/job_matches_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G187"/>
+  <dimension ref="A1:G179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4283,17 +4283,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Senior Solutions Architect - Airflow (East Coast)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Philadelphia, NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
+          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (East Coast)</t>
+          <t>Senior Software Enginnering</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Enginnering</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,59 +4381,59 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
+          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
+          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Oracle Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
+          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure Engineer</t>
+          <t>Data Engineer, Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
+          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer, Forward Deployed Engineer</t>
+          <t>OIC Platform Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
+          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>OIC Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Build-A-Bear Workshop</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Build-A-Bear Workshop</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Reno, NV, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>STORD Warehouse</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Reno, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>Glue, IAM, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
+          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Technical Solutions Engineer - Pre</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>STORD Warehouse</t>
+          <t>Verily</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Glue, IAM, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Technical Solutions Engineer - Pre</t>
+          <t>Analytics Platform Engineer Alteryx</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Verily</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Garland, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,69 +4686,69 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Analytics Platform Engineer Alteryx</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Garland, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
+          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Devops Engineer (remote)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,14 +4766,14 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
+          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Devops Engineer (remote)</t>
+          <t>DevOps Engineer (local)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
+          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DevOps Engineer (local)</t>
+          <t>Real-Time Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
+          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Real-Time Data Engineer</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hopkinton, MA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Apache Kafka Developer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Hopkinton, MA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
+          <t>https://www.indeed.com/viewjob?jk=60ffb92f7d3b11c8</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,14 +4976,14 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ffb92f7d3b11c8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Apache Kafka Developer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,19 +5011,19 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>MicroStrategy Architect</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Data Meaning</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
+          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MicroStrategy Architect</t>
+          <t>AI DevOps Engineer (Global)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Data Meaning</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
+          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Lambda, Scala, Kafka, Oracle, MySQL, MongoDB, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1b6ba41a8a56f2</t>
+          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Lambda, Scala, Kafka, Oracle, MySQL, MongoDB, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d95cae4e2d404f</t>
+          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Lambda, Scala, Kafka, Oracle, MySQL, MongoDB, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,32 +5186,32 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c221ea0da8a688bf</t>
+          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer (Global)</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
+          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Software Engineer II - Big Data &amp; AWS</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
+          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
         </is>
       </c>
     </row>
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
+          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
+          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
+          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
+          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Junior Platform Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>Clarity Innovations, LLC</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
+          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Cloud Solution Architect (Remote)</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
+          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Backend Software Engineer III</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,42 +5491,42 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
+          <t>https://www.indeed.com/viewjob?jk=efd7f5b9b5f1900d</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Senior Java Engineer with NetSuite Experience</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,32 +5536,32 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,32 +5571,32 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
+          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect (Remote)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Wellvana Health</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
+          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,32 +5606,32 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
+          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>QA Automation Engineer - Brokerage/ Financial domain</t>
+          <t>Senior Data Engineer – Platform Foundation</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Inabia Software &amp; Consulting Inc.</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,32 +5641,32 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e248d1d788eee10</t>
+          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Junior Platform Engineer</t>
+          <t>Informatica Intelligent Data Management Cloud</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Clarity Innovations, LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,32 +5676,32 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
+          <t>https://www.indeed.com/viewjob?jk=b14760973f99a8d6</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Associate Software Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Universal City, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Scala, Kafka, SQL Server, Data Modeling, Splunk, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6537fbdf744212f8</t>
+          <t>https://www.indeed.com/viewjob?jk=d97138d9df18fcba</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior Java Engineer with NetSuite Experience</t>
+          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>Engineer II, Advanced Research (Remote)</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
+          <t>https://www.indeed.com/viewjob?jk=8e40cb2a69d120f5</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Backend Software Engineer (API-focused)</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Wellvana Health</t>
+          <t>Off Duty Management</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Katy, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
+          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Platform Foundation</t>
+          <t>COE QE DevOps role - C1</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
+          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JSSA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
+          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba2d09365f6ee5a</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Informatica Intelligent Data Management Cloud</t>
+          <t>Software Engineering, Sr Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,34 +5981,34 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14760973f99a8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Specialist, Application Development</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,34 +6016,34 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba2d09365f6ee5a</t>
+          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior Associate Software Engineer</t>
+          <t>Project Controls, Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, SQL Server, Data Modeling, Splunk, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97138d9df18fcba</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f66e61d041240a</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
+          <t>Project Controls, Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,32 +6096,32 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
+          <t>https://www.indeed.com/viewjob?jk=df8062c19c4d1d41</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Engineer II, Advanced Research (Remote)</t>
+          <t>Database Developer Expert</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,32 +6131,32 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e40cb2a69d120f5</t>
+          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (API-focused)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Off Duty Management</t>
+          <t>Merck KGaA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Katy, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,32 +6166,32 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>COE QE DevOps role - C1</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,172 +6201,172 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JSSA</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
+          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
+          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Software Engineering, Sr Engineer</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
+          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior Specialist, Application Development</t>
+          <t>OpenShift Administrator</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>IT Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,32 +6376,32 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac351039409cb17</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Project Controls, Database Administrator (DBA)</t>
+          <t>Software Engineer II - SRE</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,32 +6411,32 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f66e61d041240a</t>
+          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Project Controls, Database Administrator (DBA)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df8062c19c4d1d41</t>
+          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Database Developer Expert</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Merck KGaA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6516,24 +6516,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
+          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
+          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>OpenShift Administrator</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,34 +6576,34 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
+          <t>https://www.indeed.com/viewjob?jk=aa01236e58a71dfc</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Asst Dir-DevOps Engineer</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,34 +6611,34 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
+          <t>https://www.indeed.com/viewjob?jk=4f20f826b053e576</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Software Engineer II - SRE</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Enterprise Knowledge</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
+          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Aberdeen Proving Ground, MD, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,297 +6681,17 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Defense Unicorns</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Senior Grafana Engineer</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Senior Grafana Engineer</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa01236e58a71dfc</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Java Architect</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Softpath System LLC</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Newark, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64c763f434149f33</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Enterprise Knowledge</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Dynamo Technologies</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Aberdeen Proving Ground, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=522e7d02e7987862</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Senior Tableau &amp; Alteryx Administrator (Cloud + DevOps Expertise)</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Intone Networks</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Winterville, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Redshift, Step Functions, RDS, Kafka, Tableau, Tableau Server, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=653b8eca70818820</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-17.xlsx
+++ b/results/job_matches_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G179"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Excel Sports Management</t>
+          <t>U.S. Financial Technology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, Azure, GCP, PostgreSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c48dbd46696795</t>
+          <t>https://www.indeed.com/viewjob?jk=aac712b4e1b735d4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Excel Sports Management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Vertex AI, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, Azure, GCP, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3a80ab86734aea</t>
+          <t>https://www.indeed.com/viewjob?jk=54c48dbd46696795</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Reliability Engineer</t>
+          <t>Databricks Developer (Unity Catalog Migration)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>DysrupIT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, Tableau, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b0948bec3ed1512</t>
+          <t>https://www.indeed.com/viewjob?jk=b253191bad860e34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Vertex AI, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd9b93bfe4203dee</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3a80ab86734aea</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Reliability Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, Tableau, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eda973817d320c4</t>
+          <t>https://www.indeed.com/viewjob?jk=3b0948bec3ed1512</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Application Development and Implementation Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9409951346a7ad0d</t>
+          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af009d50d9ce471a</t>
+          <t>https://www.indeed.com/viewjob?jk=bd9b93bfe4203dee</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b475180d99aecacf</t>
+          <t>https://www.indeed.com/viewjob?jk=3eda973817d320c4</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772d08b80e754e75</t>
+          <t>https://www.indeed.com/viewjob?jk=9409951346a7ad0d</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3fd193c06ae0581</t>
+          <t>https://www.indeed.com/viewjob?jk=af009d50d9ce471a</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b65c34e565b992c</t>
+          <t>https://www.indeed.com/viewjob?jk=b475180d99aecacf</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779fe138ded484b</t>
+          <t>https://www.indeed.com/viewjob?jk=772d08b80e754e75</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb1c755d148975ff</t>
+          <t>https://www.indeed.com/viewjob?jk=e3fd193c06ae0581</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613cd064c5c54a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b65c34e565b992c</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=120779d15d1fcfb6</t>
+          <t>https://www.indeed.com/viewjob?jk=0779fe138ded484b</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67914dd58a58a8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=cb1c755d148975ff</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31d4f4143f7cb28</t>
+          <t>https://www.indeed.com/viewjob?jk=613cd064c5c54a4c</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a5289604bca0cff</t>
+          <t>https://www.indeed.com/viewjob?jk=120779d15d1fcfb6</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3fe4280a2c93391</t>
+          <t>https://www.indeed.com/viewjob?jk=67914dd58a58a8d4</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae284e6548c3258</t>
+          <t>https://www.indeed.com/viewjob?jk=a31d4f4143f7cb28</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbe9517a3231d13b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a5289604bca0cff</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425185029b9803cd</t>
+          <t>https://www.indeed.com/viewjob?jk=f3fe4280a2c93391</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e4cfd7cccd7103</t>
+          <t>https://www.indeed.com/viewjob?jk=cae284e6548c3258</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee699af0925dbbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=fbe9517a3231d13b</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beebec88652a0ad1</t>
+          <t>https://www.indeed.com/viewjob?jk=425185029b9803cd</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d241129f70a15de3</t>
+          <t>https://www.indeed.com/viewjob?jk=05e4cfd7cccd7103</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811f9831e5bf2622</t>
+          <t>https://www.indeed.com/viewjob?jk=ee699af0925dbbc0</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d5324a2b8a1805</t>
+          <t>https://www.indeed.com/viewjob?jk=beebec88652a0ad1</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50f7ae8262615bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=d241129f70a15de3</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b295f641478562</t>
+          <t>https://www.indeed.com/viewjob?jk=811f9831e5bf2622</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c092bdfadcd07b8</t>
+          <t>https://www.indeed.com/viewjob?jk=48d5324a2b8a1805</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4028439241ee86b</t>
+          <t>https://www.indeed.com/viewjob?jk=50f7ae8262615bc7</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7c190952f3113a4</t>
+          <t>https://www.indeed.com/viewjob?jk=13b295f641478562</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d90ab183a51383</t>
+          <t>https://www.indeed.com/viewjob?jk=7c092bdfadcd07b8</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10752c112f86257</t>
+          <t>https://www.indeed.com/viewjob?jk=e4028439241ee86b</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523d0e5286ecdc4d</t>
+          <t>https://www.indeed.com/viewjob?jk=f7c190952f3113a4</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40492208ab43d208</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d90ab183a51383</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cd193841933bb</t>
+          <t>https://www.indeed.com/viewjob?jk=c10752c112f86257</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Hadoop/Spark/OCP/Big Data</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa14baaf9fd7957</t>
+          <t>https://www.indeed.com/viewjob?jk=523d0e5286ecdc4d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeade119569bbf7</t>
+          <t>https://www.indeed.com/viewjob?jk=40492208ab43d208</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93edda5c98f4cdb4</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cd193841933bb</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Hadoop/Spark/OCP/Big Data</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1cdcb324b377bf</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa14baaf9fd7957</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bc1107dcef567b</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeade119569bbf7</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab6ea52221dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=93edda5c98f4cdb4</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b1bb8e723d49656</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1cdcb324b377bf</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MDM Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c2c9fdda4f8d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=06bc1107dcef567b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab6ea52221dfe</t>
         </is>
       </c>
     </row>
@@ -2328,20 +2328,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f1eb8e2a6e504b</t>
+          <t>https://www.indeed.com/viewjob?jk=5b1bb8e723d49656</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MDM Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587249eddf698e94</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c2c9fdda4f8d1c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c7b5c770c1535f</t>
+          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf29b9a8949927c0</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f1eb8e2a6e504b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e9ac43a4c79de0</t>
+          <t>https://www.indeed.com/viewjob?jk=587249eddf698e94</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6f565a0cba9b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c7b5c770c1535f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93a6382b79298c2</t>
+          <t>https://www.indeed.com/viewjob?jk=bf29b9a8949927c0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c55cbc7a32077d</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e9ac43a4c79de0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bfd9be8468f66b3</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f547f3d8df9f9bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Solutions Architect - Airflow (East Coast)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>Philadelphia, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54854fd47b363a4</t>
+          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45df0d1609c8367b</t>
+          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Enginnering</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,102 +2771,102 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23bdc76018751755</t>
+          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43290df41714a389</t>
+          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Oracle Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b16b2331ee1aa84</t>
+          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer, Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b04e833dd19df0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>OIC Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259cc44945602b4</t>
+          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Build-A-Bear Workshop</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4feede92620f22e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Reno, NV, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbebd14ac0ed49c4</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>STORD Warehouse</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>Glue, IAM, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e43910adecb4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Technical Solutions Engineer - Pre</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Verily</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2756336b0144995b</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Analytics Platform Engineer Alteryx</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Garland, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41c68f32e47611a1</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd8d2e3100ea907</t>
+          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Devops Engineer (remote)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e69471258c9ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>DevOps Engineer (local)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba35650e2da9649</t>
+          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Real-Time Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb9c24b4a27b99e</t>
+          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08abb8a8067dabe</t>
+          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Hopkinton, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5c390fe780fb83</t>
+          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Apache Kafka Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10e7c9ecd47ff09</t>
+          <t>https://www.indeed.com/viewjob?jk=60ffb92f7d3b11c8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Apache Kafka Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9393aab76aef47</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de5598243142a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>MicroStrategy Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Data Meaning</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4f92e0b5a77250</t>
+          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI DevOps Engineer (Global)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b5097fd06a5b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dbcec9a2251bc8e</t>
+          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1abb06a257adfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ccd80ac908db0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09da3c6a02110e7</t>
+          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b81878d33b2cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2fc82662d2d577e</t>
+          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f11a2204aeac9</t>
+          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3733,15 +3733,15 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,14 +3751,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4bd4f9915f719</t>
+          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3768,15 +3768,15 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d99d8a28b97414</t>
+          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Junior Platform Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Clarity Innovations, LLC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e41db969f64f04</t>
+          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Cloud Solution Architect (Remote)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,67 +3856,67 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e92b6c49d12909</t>
+          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Backend Software Engineer III</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad5fe900bb21047</t>
+          <t>https://www.indeed.com/viewjob?jk=efd7f5b9b5f1900d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Java Engineer with NetSuite Experience</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6e55b5d347e590</t>
+          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4055b440fbf4926</t>
+          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wellvana Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d661b2249c160667</t>
+          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer – Platform Foundation</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7fb86315501bea</t>
+          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Informatica Intelligent Data Management Cloud</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48351a9424c5adaf</t>
+          <t>https://www.indeed.com/viewjob?jk=b14760973f99a8d6</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Associate Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Scala, Kafka, SQL Server, Data Modeling, Splunk, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=449ffea81d7dabee</t>
+          <t>https://www.indeed.com/viewjob?jk=d97138d9df18fcba</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b4c29a1cbe80d1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Specialist, Application Development</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed68905fe7cf4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Engineer II, Advanced Research (Remote)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0cd86430f84239c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e40cb2a69d120f5</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Backend Software Engineer (API-focused)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Off Duty Management</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Katy, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>COE QE DevOps role - C1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (East Coast)</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>JSSA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,19 +4311,19 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Enginnering</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4332,11 +4332,11 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,137 +4346,137 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba2d09365f6ee5a</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineering, Sr Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
+          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure Engineer</t>
+          <t>Project Controls, Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f66e61d041240a</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer, Forward Deployed Engineer</t>
+          <t>Project Controls, Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
+          <t>https://www.indeed.com/viewjob?jk=df8062c19c4d1d41</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>OIC Platform Engineer</t>
+          <t>Database Developer Expert</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,19 +4521,19 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
+          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Build-A-Bear Workshop</t>
+          <t>Merck KGaA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4542,11 +4542,11 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Reno, NV, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,102 +4591,102 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>STORD Warehouse</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Glue, IAM, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
+          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Technical Solutions Engineer - Pre</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Verily</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
+          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Analytics Platform Engineer Alteryx</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Garland, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,54 +4696,54 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
+          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>OpenShift Administrator</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Devops Engineer (remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4752,11 +4752,11 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DevOps Engineer (local)</t>
+          <t>Software Engineer II - SRE</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,19 +4801,19 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
+          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Real-Time Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4822,11 +4822,11 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Hopkinton, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
+          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Apache Kafka Developer</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ffb92f7d3b11c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Apache Kafka Developer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,102 +4976,102 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=aa01236e58a71dfc</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Asst Dir-DevOps Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
+          <t>https://www.indeed.com/viewjob?jk=4f20f826b053e576</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MicroStrategy Architect</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Data Meaning</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Aberdeen Proving Ground, MD, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
+          <t>https://www.indeed.com/viewjob?jk=522e7d02e7987862</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer (Global)</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Enterprise Knowledge</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,1617 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Software Engineer, Data Foundations</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Whatnot</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Software Engineer, Data Foundations</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Whatnot</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Software Engineer, Data Foundations</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Whatnot</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Software Engineer, Data Foundations</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Whatnot</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>EPIC Kids</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Software Engineer, Data Foundations</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Whatnot</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Senior, Data Engineer</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Carrington Mortgage Services, LLC</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Scottsdale, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Woonsocket, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Junior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Clarity Innovations, LLC</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Columbia, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Cloud Solution Architect (Remote)</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Hyatt</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Backend Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Chewy</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, DynamoDB</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=efd7f5b9b5f1900d</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Senior Java Engineer with NetSuite Experience</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Plan A Technologies</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Senior Data Platform Engineer / SDE</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Cambia Health Solutions</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Wellvana Health</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer – Platform Foundation</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Auburn Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Informatica Intelligent Data Management Cloud</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Schaumburg, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b14760973f99a8d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Senior Associate Software Engineer</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Truist</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, SQL Server, Data Modeling, Splunk, CI/CD, Jenkins, Maven, Docker</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d97138d9df18fcba</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>MiniMed</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Northridge, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Engineer II, Advanced Research (Remote)</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>MN, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e40cb2a69d120f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Backend Software Engineer (API-focused)</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Off Duty Management</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Katy, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>COE QE DevOps role - C1</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Grand Rapids, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>JSSA</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Rockville, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Simpson Strong-Tie</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Full Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Synopsys</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba2d09365f6ee5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Software Engineering, Sr Engineer</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Synopsys</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Santa Fe, NM, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Senior Specialist, Application Development</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>BNY</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Project Controls, Database Administrator (DBA)</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f66e61d041240a</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Project Controls, Database Administrator (DBA)</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Columbia, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df8062c19c4d1d41</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Database Developer Expert</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Experian</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Merck KGaA</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Pacific Life</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Senior AWS Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>New Era Technology</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Senior AWS Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>New Era Technology</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Senior AWS Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>New Era Technology</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>OpenShift Administrator</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>BNY</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Software Engineer II - SRE</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Honeywell</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Township of Hamilton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Defense Unicorns</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Defense Unicorns</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Senior Grafana Engineer</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Senior Grafana Engineer</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa01236e58a71dfc</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Asst Dir-DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Moody's</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f20f826b053e576</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Enterprise Knowledge</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Dynamo Technologies</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Aberdeen Proving Ground, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=522e7d02e7987862</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-17.xlsx
+++ b/results/job_matches_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MDM Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeade119569bbf7</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c2c9fdda4f8d1c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93edda5c98f4cdb4</t>
+          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
         </is>
       </c>
     </row>
@@ -2223,20 +2223,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1cdcb324b377bf</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f1eb8e2a6e504b</t>
         </is>
       </c>
     </row>
@@ -2258,20 +2258,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bc1107dcef567b</t>
+          <t>https://www.indeed.com/viewjob?jk=587249eddf698e94</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab6ea52221dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c7b5c770c1535f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b1bb8e723d49656</t>
+          <t>https://www.indeed.com/viewjob?jk=bf29b9a8949927c0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MDM Architect</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,19 +2386,19 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c2c9fdda4f8d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e9ac43a4c79de0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f1eb8e2a6e504b</t>
+          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Enginnering</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587249eddf698e94</t>
+          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Solutions Architect - Airflow (East Coast)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Philadelphia, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c7b5c770c1535f</t>
+          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,54 +2561,54 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf29b9a8949927c0</t>
+          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e9ac43a4c79de0</t>
+          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Oracle Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2617,46 +2617,46 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Data Engineer, Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (East Coast)</t>
+          <t>OIC Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Build-A-Bear Workshop</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Enginnering</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Reno, NV, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>STORD Warehouse</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>Glue, IAM, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
+          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure Engineer</t>
+          <t>Technical Solutions Engineer - Pre</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Verily</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer, Forward Deployed Engineer</t>
+          <t>Analytics Platform Engineer Alteryx</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Garland, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,24 +2866,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>OIC Platform Engineer</t>
+          <t>Streaming Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2897,46 +2897,46 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
+          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Build-A-Bear Workshop</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
+          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Devops Engineer (remote)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Reno, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
+          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>DevOps Engineer (local)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>STORD Warehouse</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Glue, IAM, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
+          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Technical Solutions Engineer - Pre</t>
+          <t>Real-Time Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Verily</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,59 +3051,59 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
+          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Analytics Platform Engineer Alteryx</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Garland, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
+          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Hopkinton, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
+          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Devops Engineer (remote)</t>
+          <t>Senior Associate - Analytics Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
+          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DevOps Engineer (local)</t>
+          <t>Apache Kafka Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
+          <t>https://www.indeed.com/viewjob?jk=60ffb92f7d3b11c8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Real-Time Data Engineer</t>
+          <t>Apache Kafka Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>MicroStrategy Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Data Meaning</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hopkinton, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
+          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Apache Kafka Developer</t>
+          <t>AI DevOps Engineer (Global)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ffb92f7d3b11c8</t>
+          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Apache Kafka Developer</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
+          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MicroStrategy Architect</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Data Meaning</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer (Global)</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
+          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
+          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
+          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
+          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
+          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Junior Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Clarity Innovations, LLC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
+          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Cloud Solution Architect (Remote)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
+          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Backend Software Engineer III</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,42 +3741,42 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=efd7f5b9b5f1900d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Senior Java Engineer with NetSuite Experience</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
+          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Junior Platform Engineer</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Clarity Innovations, LLC</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
+          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect (Remote)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Wellvana Health</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
+          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,59 +3856,59 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
+          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III</t>
+          <t>Senior Data Engineer – Platform Foundation</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efd7f5b9b5f1900d</t>
+          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Java Engineer with NetSuite Experience</t>
+          <t>Informatica Intelligent Data Management Cloud</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
+          <t>https://www.indeed.com/viewjob?jk=b14760973f99a8d6</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>Senior Associate Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>RDS, Scala, Kafka, SQL Server, Data Modeling, Splunk, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
+          <t>https://www.indeed.com/viewjob?jk=d97138d9df18fcba</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Wellvana Health</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Platform Foundation</t>
+          <t>Engineer II, Advanced Research (Remote)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e40cb2a69d120f5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Informatica Intelligent Data Management Cloud</t>
+          <t>Backend Software Engineer (API-focused)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Off Duty Management</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Katy, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14760973f99a8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Associate Software Engineer</t>
+          <t>COE QE DevOps role - C1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, SQL Server, Data Modeling, Splunk, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97138d9df18fcba</t>
+          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>JSSA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
+          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Specialist, Application Development</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Engineer II, Advanced Research (Remote)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e40cb2a69d120f5</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba2d09365f6ee5a</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (API-focused)</t>
+          <t>Software Engineering, Sr Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Off Duty Management</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Katy, TX, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>COE QE DevOps role - C1</t>
+          <t>Senior Specialist, Application Development</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
+          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Project Controls, Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>JSSA</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f66e61d041240a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Project Controls, Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,102 +4346,102 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
+          <t>https://www.indeed.com/viewjob?jk=df8062c19c4d1d41</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Database Developer Expert</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba2d09365f6ee5a</t>
+          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineering, Sr Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>Merck KGaA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Project Controls, Database Administrator (DBA)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,59 +4451,59 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f66e61d041240a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Project Controls, Database Administrator (DBA)</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df8062c19c4d1d41</t>
+          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Database Developer Expert</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
+          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Merck KGaA</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
+          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>OpenShift Administrator</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Software Engineer II - SRE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
+          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
+          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>OpenShift Administrator</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
+          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Software Engineer II - SRE</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
+          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Asst Dir-DevOps Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
+          <t>https://www.indeed.com/viewjob?jk=4f20f826b053e576</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
+          <t>https://www.indeed.com/viewjob?jk=aa01236e58a71dfc</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Grafana Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Enterprise Knowledge</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Grafana Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Aberdeen Proving Ground, MD, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,157 +4931,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa01236e58a71dfc</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Asst Dir-DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Moody's</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f20f826b053e576</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Dynamo Technologies</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Aberdeen Proving Ground, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=522e7d02e7987862</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Enterprise Knowledge</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-17.xlsx
+++ b/results/job_matches_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,25 +783,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Reliability Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Vertex AI, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, Tableau, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3a80ab86734aea</t>
+          <t>https://www.indeed.com/viewjob?jk=3b0948bec3ed1512</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Reliability Engineer</t>
+          <t>Application Development and Implementation Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, Tableau, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b0948bec3ed1512</t>
+          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Application Development and Implementation Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
+          <t>https://www.indeed.com/viewjob?jk=bd9b93bfe4203dee</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd9b93bfe4203dee</t>
+          <t>https://www.indeed.com/viewjob?jk=3eda973817d320c4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eda973817d320c4</t>
+          <t>https://www.indeed.com/viewjob?jk=9409951346a7ad0d</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9409951346a7ad0d</t>
+          <t>https://www.indeed.com/viewjob?jk=af009d50d9ce471a</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af009d50d9ce471a</t>
+          <t>https://www.indeed.com/viewjob?jk=b475180d99aecacf</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b475180d99aecacf</t>
+          <t>https://www.indeed.com/viewjob?jk=772d08b80e754e75</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772d08b80e754e75</t>
+          <t>https://www.indeed.com/viewjob?jk=e3fd193c06ae0581</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3fd193c06ae0581</t>
+          <t>https://www.indeed.com/viewjob?jk=2b65c34e565b992c</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b65c34e565b992c</t>
+          <t>https://www.indeed.com/viewjob?jk=0779fe138ded484b</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779fe138ded484b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb1c755d148975ff</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb1c755d148975ff</t>
+          <t>https://www.indeed.com/viewjob?jk=613cd064c5c54a4c</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613cd064c5c54a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=120779d15d1fcfb6</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=120779d15d1fcfb6</t>
+          <t>https://www.indeed.com/viewjob?jk=67914dd58a58a8d4</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67914dd58a58a8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=a31d4f4143f7cb28</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31d4f4143f7cb28</t>
+          <t>https://www.indeed.com/viewjob?jk=4a5289604bca0cff</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a5289604bca0cff</t>
+          <t>https://www.indeed.com/viewjob?jk=f3fe4280a2c93391</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3fe4280a2c93391</t>
+          <t>https://www.indeed.com/viewjob?jk=cae284e6548c3258</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae284e6548c3258</t>
+          <t>https://www.indeed.com/viewjob?jk=fbe9517a3231d13b</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbe9517a3231d13b</t>
+          <t>https://www.indeed.com/viewjob?jk=425185029b9803cd</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425185029b9803cd</t>
+          <t>https://www.indeed.com/viewjob?jk=05e4cfd7cccd7103</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e4cfd7cccd7103</t>
+          <t>https://www.indeed.com/viewjob?jk=ee699af0925dbbc0</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee699af0925dbbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=beebec88652a0ad1</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beebec88652a0ad1</t>
+          <t>https://www.indeed.com/viewjob?jk=d241129f70a15de3</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d241129f70a15de3</t>
+          <t>https://www.indeed.com/viewjob?jk=811f9831e5bf2622</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811f9831e5bf2622</t>
+          <t>https://www.indeed.com/viewjob?jk=48d5324a2b8a1805</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d5324a2b8a1805</t>
+          <t>https://www.indeed.com/viewjob?jk=50f7ae8262615bc7</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50f7ae8262615bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=13b295f641478562</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b295f641478562</t>
+          <t>https://www.indeed.com/viewjob?jk=7c092bdfadcd07b8</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c092bdfadcd07b8</t>
+          <t>https://www.indeed.com/viewjob?jk=e4028439241ee86b</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4028439241ee86b</t>
+          <t>https://www.indeed.com/viewjob?jk=f7c190952f3113a4</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7c190952f3113a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d90ab183a51383</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d90ab183a51383</t>
+          <t>https://www.indeed.com/viewjob?jk=c10752c112f86257</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10752c112f86257</t>
+          <t>https://www.indeed.com/viewjob?jk=523d0e5286ecdc4d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523d0e5286ecdc4d</t>
+          <t>https://www.indeed.com/viewjob?jk=40492208ab43d208</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40492208ab43d208</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cd193841933bb</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Senior Data Engineer - Hadoop/Spark/OCP/Big Data</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cd193841933bb</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa14baaf9fd7957</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Hadoop/Spark/OCP/Big Data</t>
+          <t>MDM Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa14baaf9fd7957</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c2c9fdda4f8d1c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MDM Architect</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c2c9fdda4f8d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f1eb8e2a6e504b</t>
         </is>
       </c>
     </row>
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f1eb8e2a6e504b</t>
+          <t>https://www.indeed.com/viewjob?jk=587249eddf698e94</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587249eddf698e94</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c7b5c770c1535f</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c7b5c770c1535f</t>
+          <t>https://www.indeed.com/viewjob?jk=bf29b9a8949927c0</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf29b9a8949927c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e9ac43a4c79de0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Business Systems Analyst</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Infoville, Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e9ac43a4c79de0</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d7fde96960560b</t>
         </is>
       </c>
     </row>
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Enginnering</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
+          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (East Coast)</t>
+          <t>Senior Software Enginnering</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
         </is>
       </c>
     </row>
@@ -2568,52 +2568,52 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Solutions Architect - Airflow (East Coast)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Philadelphia, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
+          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>pointer infotech L.L.C</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
+          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer, Forward Deployed Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,24 +2656,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
+          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>OIC Platform Engineer</t>
+          <t>Oracle Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2696,29 +2696,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
+          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Build-A-Bear Workshop</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
+          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>OIC Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Reno, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
+          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>STORD Warehouse</t>
+          <t>Build-A-Bear Workshop</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Glue, IAM, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Technical Solutions Engineer - Pre</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Verily</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Reno, NV, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Analytics Platform Engineer Alteryx</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>STORD Warehouse</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Garland, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,164 +2866,164 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
+          <t>Glue, IAM, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
+          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Streaming Data Engineer</t>
+          <t>Technical Solutions Engineer - Pre</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Verily</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Sr. Solutions Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Devops Engineer (remote)</t>
+          <t>Sr. Solutions Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba9b17426b74a1b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DevOps Engineer (local)</t>
+          <t>Analytics Platform Engineer Alteryx</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Garland, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Real-Time Data Engineer</t>
+          <t>Streaming Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3046,29 +3046,29 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Devops Engineer (remote)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hopkinton, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
+          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Associate - Analytics Engineer</t>
+          <t>DevOps Engineer (local)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,24 +3146,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
+          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Apache Kafka Developer</t>
+          <t>Real-Time Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ffb92f7d3b11c8</t>
+          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Apache Kafka Developer</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hopkinton, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
+          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MicroStrategy Architect</t>
+          <t>Senior Associate - Analytics Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Data Meaning</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer (Global)</t>
+          <t>Apache Kafka Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
+          <t>https://www.indeed.com/viewjob?jk=60ffb92f7d3b11c8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Apache Kafka Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
+          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>MicroStrategy Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Data Meaning</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
+          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>AI DevOps Engineer (Global)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
+          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
+          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
+          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
+          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
+          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Junior Platform Engineer</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Clarity Innovations, LLC</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
+          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect (Remote)</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
+          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,42 +3741,42 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efd7f5b9b5f1900d</t>
+          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Java Engineer with NetSuite Experience</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
+          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>Junior Platform Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Clarity Innovations, LLC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
+          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud Solution Architect (Remote)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Wellvana Health</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,59 +3856,59 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
+          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Platform Foundation</t>
+          <t>Backend Software Engineer III</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
+          <t>https://www.indeed.com/viewjob?jk=efd7f5b9b5f1900d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Informatica Intelligent Data Management Cloud</t>
+          <t>Senior Java Engineer with NetSuite Experience</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14760973f99a8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Associate Software Engineer</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, SQL Server, Data Modeling, Splunk, CI/CD, Jenkins, Maven, Docker</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97138d9df18fcba</t>
+          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Wellvana Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
+          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
+          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Engineer II, Advanced Research (Remote)</t>
+          <t>Senior Data Engineer – Platform Foundation</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e40cb2a69d120f5</t>
+          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (API-focused)</t>
+          <t>Informatica Intelligent Data Management Cloud</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Off Duty Management</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Katy, TX, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=b14760973f99a8d6</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>COE QE DevOps role - C1</t>
+          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Engineer II, Advanced Research (Remote)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JSSA</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
+          <t>https://www.indeed.com/viewjob?jk=8e40cb2a69d120f5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Backend Software Engineer (API-focused)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>Off Duty Management</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Katy, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
+          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>COE QE DevOps role - C1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba2d09365f6ee5a</t>
+          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineering, Sr Engineer</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>JSSA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
+          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Specialist, Application Development</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Project Controls, Database Administrator (DBA)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f66e61d041240a</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba2d09365f6ee5a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Project Controls, Database Administrator (DBA)</t>
+          <t>Software Engineering, Sr Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,42 +4336,42 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df8062c19c4d1d41</t>
+          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Database Developer Expert</t>
+          <t>Senior Specialist, Application Development</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
+          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Database Developer Expert</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Merck KGaA</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
+          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Merck KGaA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,17 +4476,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
+          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
+          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>OpenShift Administrator</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,19 +4591,19 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
+          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>OpenShift Administrator</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer II - SRE</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II - SRE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
+          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
+          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Grafana Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
         </is>
       </c>
     </row>
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
+          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Asst Dir-DevOps Engineer</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,17 +4826,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f20f826b053e576</t>
+          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
         </is>
       </c>
     </row>
@@ -4878,17 +4878,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Enterprise Knowledge</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>.NET Engineer with Dicom</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Dynamo Technologies</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Aberdeen Proving Ground, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,17 +4931,157 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Dynamo Technologies</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Aberdeen Proving Ground, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=522e7d02e7987862</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Ai Engineer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Johnson Controls</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Asst Dir-DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f20f826b053e576</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-17.xlsx
+++ b/results/job_matches_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Meso Scale Diagnostics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=387fc6b51ae76f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=040188cbf02542cc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -631,19 +631,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12d58810cbcb954b</t>
+          <t>https://www.indeed.com/viewjob?jk=387fc6b51ae76f3d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Platform Specialist</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30dc1ebf3576193b</t>
+          <t>https://www.indeed.com/viewjob?jk=12d58810cbcb954b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>AWS Platform Specialist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U.S. Financial Technology</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aac712b4e1b735d4</t>
+          <t>https://www.indeed.com/viewjob?jk=30dc1ebf3576193b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Excel Sports Management</t>
+          <t>U.S. Financial Technology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, Azure, GCP, PostgreSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c48dbd46696795</t>
+          <t>https://www.indeed.com/viewjob?jk=aac712b4e1b735d4</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Application Development and Implementation Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Bloomerang</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0fe96b9bdbba45</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Application Development and Implementation Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd9b93bfe4203dee</t>
+          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Hadoop/Spark/OCP/Big Data</t>
+          <t>MDM Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa14baaf9fd7957</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c2c9fdda4f8d1c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MDM Architect</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,59 +2141,59 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c2c9fdda4f8d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Data and Cloud Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
+          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f1eb8e2a6e504b</t>
+          <t>https://www.indeed.com/viewjob?jk=1da4ecc01920f955</t>
         </is>
       </c>
     </row>
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587249eddf698e94</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f1eb8e2a6e504b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c7b5c770c1535f</t>
+          <t>https://www.indeed.com/viewjob?jk=587249eddf698e94</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Business Systems Analyst</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Infoville, Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,42 +2306,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf29b9a8949927c0</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d7fde96960560b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,54 +2351,54 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e9ac43a4c79de0</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Business Systems Analyst</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Infoville, Inc</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d7fde96960560b</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
+          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Software Enginnering</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,19 +2456,19 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,129 +2491,129 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Enginnering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>pointer infotech L.L.C</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
+          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
+          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (East Coast)</t>
+          <t>Oracle Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>pointer infotech L.L.C</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
+          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>OIC Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
+          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Build-A-Bear Workshop</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer, Forward Deployed Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Reno, NV, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,19 +2736,19 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>OIC Platform Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>STORD Warehouse</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>Glue, IAM, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
+          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Solutions Engineer - Pre</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Build-A-Bear Workshop</t>
+          <t>Verily</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Solutions Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Reno, NV, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr. Solutions Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>STORD Warehouse</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Glue, IAM, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba9b17426b74a1b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Technical Solutions Engineer - Pre</t>
+          <t>Analytics Platform Engineer Alteryx</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Verily</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Garland, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect</t>
+          <t>Streaming Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,94 +2946,94 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
+          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba9b17426b74a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Analytics Platform Engineer Alteryx</t>
+          <t>Devops Engineer (remote)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Garland, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
+          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Streaming Data Engineer</t>
+          <t>DevOps Engineer (local)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
+          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Real-Time Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
+          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Devops Engineer (remote)</t>
+          <t>Senior Associate - Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
+          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DevOps Engineer (local)</t>
+          <t>Apache Kafka Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
+          <t>https://www.indeed.com/viewjob?jk=60ffb92f7d3b11c8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Real-Time Data Engineer</t>
+          <t>Apache Kafka Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hopkinton, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
+          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Associate - Analytics Engineer</t>
+          <t>MicroStrategy Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Data Meaning</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
+          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Apache Kafka Developer</t>
+          <t>AI DevOps Engineer (Global)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ffb92f7d3b11c8</t>
+          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Apache Kafka Developer</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
+          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MicroStrategy Architect</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Data Meaning</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer (Global)</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
+          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
+          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
+          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
+          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
+          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Junior Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Clarity Innovations, LLC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
+          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Cloud Solution Architect (Remote)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
+          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Backend Software Engineer III</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,42 +3741,42 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=efd7f5b9b5f1900d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Senior Java Engineer with NetSuite Experience</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
+          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Junior Platform Engineer</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Clarity Innovations, LLC</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
+          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect (Remote)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Wellvana Health</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
+          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,59 +3856,59 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
+          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III</t>
+          <t>Senior Data Engineer – Platform Foundation</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efd7f5b9b5f1900d</t>
+          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Java Engineer with NetSuite Experience</t>
+          <t>Informatica Intelligent Data Management Cloud</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
+          <t>https://www.indeed.com/viewjob?jk=b14760973f99a8d6</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>Engineer II, Advanced Research (Remote)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
+          <t>https://www.indeed.com/viewjob?jk=8e40cb2a69d120f5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Backend Software Engineer (API-focused)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Wellvana Health</t>
+          <t>Off Duty Management</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Katy, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
+          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Platform Foundation</t>
+          <t>COE QE DevOps role - C1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
+          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Informatica Intelligent Data Management Cloud</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JSSA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14760973f99a8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
         </is>
       </c>
     </row>
@@ -4108,17 +4108,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Engineer II, Advanced Research (Remote)</t>
+          <t>Senior Specialist, Application Development</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e40cb2a69d120f5</t>
+          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (API-focused)</t>
+          <t>Database Developer Expert</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Off Duty Management</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Katy, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>COE QE DevOps role - C1</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Merck KGaA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>JSSA</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,164 +4241,164 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
+          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba2d09365f6ee5a</t>
+          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineering, Sr Engineer</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
+          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Specialist, Application Development</t>
+          <t>OpenShift Administrator</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Database Developer Expert</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II - SRE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Merck KGaA</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
+          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
+          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
+          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
+          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Senior Full Stack Java Architect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Softpath System LLC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
+          <t>https://www.indeed.com/viewjob?jk=fe74c0137bb982fb</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>OpenShift Administrator</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
+          <t>https://www.indeed.com/viewjob?jk=aa01236e58a71dfc</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer II - SRE</t>
+          <t>.NET Engineer with Dicom</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
+          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>Enterprise Knowledge</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
+          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Ai Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
+          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Grafana Engineer</t>
+          <t>Asst Dir-DevOps Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,295 +4791,15 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Senior Grafana Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa01236e58a71dfc</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>.NET Engineer with Dicom</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Digital Dhara LLC</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Enterprise Knowledge</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Dynamo Technologies</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Aberdeen Proving Ground, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=522e7d02e7987862</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Ai Engineer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Johnson Controls</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Asst Dir-DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Moody's</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4f20f826b053e576</t>
         </is>

--- a/results/job_matches_2026-07-17.xlsx
+++ b/results/job_matches_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,95 +538,95 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>Nitor Infotech</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>25</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, clustering keys</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Azure, Blob Storage, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba13c042faeff40f</t>
+          <t>https://www.indeed.com/viewjob?jk=9691a4b3c751e344</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Meso Scale Diagnostics</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.5</v>
+        <v>22.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, Databricks, BigQuery</t>
+          <t>AWS, S3, RDS, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, clustering keys</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=040188cbf02542cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba13c042faeff40f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Meso Scale Diagnostics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=387fc6b51ae76f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=040188cbf02542cc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -666,19 +666,19 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12d58810cbcb954b</t>
+          <t>https://www.indeed.com/viewjob?jk=387fc6b51ae76f3d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Platform Specialist</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30dc1ebf3576193b</t>
+          <t>https://www.indeed.com/viewjob?jk=12d58810cbcb954b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>AWS Platform Specialist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U.S. Financial Technology</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aac712b4e1b735d4</t>
+          <t>https://www.indeed.com/viewjob?jk=30dc1ebf3576193b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Developer (Unity Catalog Migration)</t>
+          <t>Site Reliability Engineer ll</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DysrupIT</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, SQS, SNS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b253191bad860e34</t>
+          <t>https://www.indeed.com/viewjob?jk=72289279cfc2dcd3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Reliability Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>U.S. Financial Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, Tableau, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b0948bec3ed1512</t>
+          <t>https://www.indeed.com/viewjob?jk=aac712b4e1b735d4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Databricks Developer (Unity Catalog Migration)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bloomerang</t>
+          <t>DysrupIT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -832,38 +832,38 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0fe96b9bdbba45</t>
+          <t>https://www.indeed.com/viewjob?jk=b253191bad860e34</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Application Development and Implementation Engineer</t>
+          <t>Reliability Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,29 +871,29 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, Tableau, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
+          <t>https://www.indeed.com/viewjob?jk=3b0948bec3ed1512</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Bloomerang</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -906,77 +906,77 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eda973817d320c4</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0fe96b9bdbba45</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Application Development and Implementation Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9409951346a7ad0d</t>
+          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af009d50d9ce471a</t>
+          <t>https://www.indeed.com/viewjob?jk=3eda973817d320c4</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b475180d99aecacf</t>
+          <t>https://www.indeed.com/viewjob?jk=9409951346a7ad0d</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772d08b80e754e75</t>
+          <t>https://www.indeed.com/viewjob?jk=af009d50d9ce471a</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3fd193c06ae0581</t>
+          <t>https://www.indeed.com/viewjob?jk=b475180d99aecacf</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b65c34e565b992c</t>
+          <t>https://www.indeed.com/viewjob?jk=772d08b80e754e75</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779fe138ded484b</t>
+          <t>https://www.indeed.com/viewjob?jk=e3fd193c06ae0581</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb1c755d148975ff</t>
+          <t>https://www.indeed.com/viewjob?jk=2b65c34e565b992c</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613cd064c5c54a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=0779fe138ded484b</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=120779d15d1fcfb6</t>
+          <t>https://www.indeed.com/viewjob?jk=cb1c755d148975ff</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67914dd58a58a8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=613cd064c5c54a4c</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31d4f4143f7cb28</t>
+          <t>https://www.indeed.com/viewjob?jk=120779d15d1fcfb6</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a5289604bca0cff</t>
+          <t>https://www.indeed.com/viewjob?jk=67914dd58a58a8d4</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3fe4280a2c93391</t>
+          <t>https://www.indeed.com/viewjob?jk=a31d4f4143f7cb28</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae284e6548c3258</t>
+          <t>https://www.indeed.com/viewjob?jk=4a5289604bca0cff</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbe9517a3231d13b</t>
+          <t>https://www.indeed.com/viewjob?jk=f3fe4280a2c93391</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425185029b9803cd</t>
+          <t>https://www.indeed.com/viewjob?jk=cae284e6548c3258</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e4cfd7cccd7103</t>
+          <t>https://www.indeed.com/viewjob?jk=fbe9517a3231d13b</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee699af0925dbbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=425185029b9803cd</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beebec88652a0ad1</t>
+          <t>https://www.indeed.com/viewjob?jk=05e4cfd7cccd7103</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d241129f70a15de3</t>
+          <t>https://www.indeed.com/viewjob?jk=ee699af0925dbbc0</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811f9831e5bf2622</t>
+          <t>https://www.indeed.com/viewjob?jk=beebec88652a0ad1</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d5324a2b8a1805</t>
+          <t>https://www.indeed.com/viewjob?jk=d241129f70a15de3</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50f7ae8262615bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=811f9831e5bf2622</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b295f641478562</t>
+          <t>https://www.indeed.com/viewjob?jk=48d5324a2b8a1805</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c092bdfadcd07b8</t>
+          <t>https://www.indeed.com/viewjob?jk=50f7ae8262615bc7</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4028439241ee86b</t>
+          <t>https://www.indeed.com/viewjob?jk=13b295f641478562</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7c190952f3113a4</t>
+          <t>https://www.indeed.com/viewjob?jk=7c092bdfadcd07b8</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d90ab183a51383</t>
+          <t>https://www.indeed.com/viewjob?jk=e4028439241ee86b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10752c112f86257</t>
+          <t>https://www.indeed.com/viewjob?jk=f7c190952f3113a4</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523d0e5286ecdc4d</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d90ab183a51383</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40492208ab43d208</t>
+          <t>https://www.indeed.com/viewjob?jk=c10752c112f86257</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cd193841933bb</t>
+          <t>https://www.indeed.com/viewjob?jk=523d0e5286ecdc4d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MDM Architect</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c2c9fdda4f8d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=40492208ab43d208</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,59 +2141,59 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cd193841933bb</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data and Cloud Engineer</t>
+          <t>MDM Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Zookeeper, YARN</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c2c9fdda4f8d1c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Data and Cloud Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da4ecc01920f955</t>
+          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f1eb8e2a6e504b</t>
+          <t>https://www.indeed.com/viewjob?jk=1da4ecc01920f955</t>
         </is>
       </c>
     </row>
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587249eddf698e94</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f1eb8e2a6e504b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Business Systems Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Infoville, Inc</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,52 +2306,52 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d7fde96960560b</t>
+          <t>https://www.indeed.com/viewjob?jk=587249eddf698e94</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Business Systems Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Infoville, Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d7fde96960560b</t>
         </is>
       </c>
     </row>
@@ -2386,19 +2386,19 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Enginnering</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,29 +2446,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
+          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,42 +2491,42 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
+          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>pointer infotech L.L.C</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
+          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
         </is>
       </c>
     </row>
@@ -2538,12 +2538,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>pointer infotech L.L.C</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
+          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
+          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer, Forward Deployed Engineer</t>
+          <t>Oracle Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
+          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OIC Platform Engineer</t>
+          <t>Data Engineer, Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
+          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>OIC Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Build-A-Bear Workshop</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
+          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>Build-A-Bear Workshop</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Reno, NV, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>STORD Warehouse</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reno, NV, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Glue, IAM, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Technical Solutions Engineer - Pre</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Verily</t>
+          <t>STORD Warehouse</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>Glue, IAM, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
+          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect</t>
+          <t>Technical Solutions Engineer - Pre</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Verily</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba9b17426b74a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b9675535a55f10</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Analytics Platform Engineer Alteryx</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Garland, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Streaming Data Engineer</t>
+          <t>Sr. Solutions Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,54 +2946,54 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba9b17426b74a1b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Analytics Platform Engineer Alteryx</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Garland, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Devops Engineer (remote)</t>
+          <t>Streaming Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
+          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DevOps Engineer (local)</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,19 +3051,19 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
+          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Real-Time Data Engineer</t>
+          <t>Devops Engineer (remote)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Associate - Analytics Engineer</t>
+          <t>DevOps Engineer (local)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,24 +3111,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
+          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Apache Kafka Developer</t>
+          <t>Real-Time Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ffb92f7d3b11c8</t>
+          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Apache Kafka Developer</t>
+          <t>Senior Associate - Analytics Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,14 +3226,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3256,29 +3256,29 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
+          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MicroStrategy Architect</t>
+          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Data Meaning</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
+          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer (Global)</t>
+          <t>Apache Kafka Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
+          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>MicroStrategy Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Data Meaning</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,59 +3401,59 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
+          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
+          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
+          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
+          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
         </is>
       </c>
     </row>
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
+          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
+          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
+          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Junior Platform Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Clarity Innovations, LLC</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
+          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect (Remote)</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
+          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,42 +3741,42 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efd7f5b9b5f1900d</t>
+          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Java Engineer with NetSuite Experience</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
+          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>Junior Platform Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Clarity Innovations, LLC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
+          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud Solution Architect (Remote)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Wellvana Health</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
+          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Platform Foundation</t>
+          <t>Senior Java Engineer with NetSuite Experience</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Informatica Intelligent Data Management Cloud</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14760973f99a8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Engineer II, Advanced Research (Remote)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Wellvana Health</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e40cb2a69d120f5</t>
+          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (API-focused)</t>
+          <t>Senior Data Engineer – Platform Foundation</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Off Duty Management</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Katy, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>COE QE DevOps role - C1</t>
+          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
+          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JSSA</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
+          <t>Senior Specialist, Application Development</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
+          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Specialist, Application Development</t>
+          <t>Backend Software Engineer (API-focused)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Off Duty Management</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Katy, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Database Developer Expert</t>
+          <t>COE QE DevOps role - C1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
+          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Merck KGaA</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
+          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Database Developer Expert</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
+          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Merck KGaA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, ETL, ELT, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
+          <t>https://www.indeed.com/viewjob?jk=c5a20dc79ac25721</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>OpenShift Administrator</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
+          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
+          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer II - SRE</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,29 +4441,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
+          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>OpenShift Administrator</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Grafana Engineer</t>
+          <t>Software Engineer II - SRE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Softpath System LLC</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe74c0137bb982fb</t>
+          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa01236e58a71dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Full Stack Java Architect</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Softpath System LLC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
+          <t>https://www.indeed.com/viewjob?jk=fe74c0137bb982fb</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>.NET Engineer with Dicom</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
+          <t>https://www.indeed.com/viewjob?jk=aa01236e58a71dfc</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Senior Full Stack Engineer (Payments)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Enterprise Knowledge</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
+          <t>https://www.indeed.com/viewjob?jk=096faff176ae84dc</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Ai Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Asst Dir-DevOps Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>International SOS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,15 +4791,155 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Data Modeling, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0629dbf3bccdd418</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>.NET Engineer with Dicom</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Digital Dhara LLC</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Ai Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Johnson Controls</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Asst Dir-DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
           <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4f20f826b053e576</t>
         </is>

--- a/results/job_matches_2026-07-17.xlsx
+++ b/results/job_matches_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2358,12 +2358,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
+          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
         </is>
       </c>
     </row>
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Technical Solutions Engineer - Pre</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Verily</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b9675535a55f10</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b9675535a55f10</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BrightVine Solutions</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
+          <t>https://www.indeed.com/viewjob?jk=24293ea9e15ad0ca</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect</t>
+          <t>Analytics Platform Engineer Alteryx</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Garland, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba9b17426b74a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Analytics Platform Engineer Alteryx</t>
+          <t>Streaming Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Garland, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
+          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Streaming Data Engineer</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
+          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Devops Engineer (remote)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
+          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Devops Engineer (remote)</t>
+          <t>DevOps Engineer (local)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
+          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DevOps Engineer (local)</t>
+          <t>Real-Time Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
+          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Real-Time Data Engineer</t>
+          <t>Senior Associate - Analytics Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Associate - Analytics Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,24 +3181,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
+          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
+          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
+          <t>Apache Kafka Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Apache Kafka Developer</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
         </is>
       </c>
     </row>
@@ -3408,25 +3408,25 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
+          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
+          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
+          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
+          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
+          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
+          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
+          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
+          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Junior Platform Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Clarity Innovations, LLC</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
+          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Junior Platform Engineer</t>
+          <t>Cloud Solution Architect (Remote)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Clarity Innovations, LLC</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
+          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect (Remote)</t>
+          <t>Senior Data Engineer – Platform Foundation</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
+          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Java Engineer with NetSuite Experience</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>Wellvana Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
+          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>Senior Java Engineer with NetSuite Experience</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
+          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Wellvana Health</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
+          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Platform Foundation</t>
+          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
+          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
+          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
+          <t>Backend Software Engineer (API-focused)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Off Duty Management</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Katy, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
+          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
         </is>
       </c>
     </row>
@@ -4108,87 +4108,87 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (API-focused)</t>
+          <t>Founding Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Off Duty Management</t>
+          <t>Patient Funding Alternatives</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Katy, TX, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>COE QE DevOps role - C1</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, ETL, ELT, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5a20dc79ac25721</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
+          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Database Developer Expert</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
+          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Merck KGaA</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
+          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>OpenShift Administrator</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, ETL, ELT, Git, Python, SQL</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5a20dc79ac25721</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Software Engineer II - SRE</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
+          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
+          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>OpenShift Administrator</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
+          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer II - SRE</t>
+          <t>Database Developer Expert</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
+          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
         </is>
       </c>
     </row>
@@ -4568,12 +4568,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>Merck KGaA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Java Architect</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>Softpath System LLC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
+          <t>https://www.indeed.com/viewjob?jk=fe74c0137bb982fb</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Architect</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Softpath System LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe74c0137bb982fb</t>
+          <t>https://www.indeed.com/viewjob?jk=aa01236e58a71dfc</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Senior Full Stack Engineer (Payments)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa01236e58a71dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=096faff176ae84dc</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Payments)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096faff176ae84dc</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>.NET Engineer with Dicom</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
+          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>International SOS</t>
+          <t>Enterprise Knowledge</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0629dbf3bccdd418</t>
+          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>.NET Engineer with Dicom</t>
+          <t>Ai Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
+          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Asst Dir-DevOps Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Enterprise Knowledge</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,85 +4861,15 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Ai Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Johnson Controls</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Asst Dir-DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Moody's</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4f20f826b053e576</t>
         </is>

--- a/results/job_matches_2026-07-17.xlsx
+++ b/results/job_matches_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Meso Scale Diagnostics</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.5</v>
+        <v>22.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, Databricks, BigQuery</t>
+          <t>IAM, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Oozie, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=040188cbf02542cc</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed5e67a7bd26cdb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Meso Scale Diagnostics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=387fc6b51ae76f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=040188cbf02542cc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,19 +701,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12d58810cbcb954b</t>
+          <t>https://www.indeed.com/viewjob?jk=387fc6b51ae76f3d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Platform Specialist</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30dc1ebf3576193b</t>
+          <t>https://www.indeed.com/viewjob?jk=12d58810cbcb954b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer ll</t>
+          <t>AWS Platform Specialist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, SQS, SNS, ECS, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72289279cfc2dcd3</t>
+          <t>https://www.indeed.com/viewjob?jk=30dc1ebf3576193b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Site Reliability Engineer ll</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U.S. Financial Technology</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,29 +801,29 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, SQS, SNS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aac712b4e1b735d4</t>
+          <t>https://www.indeed.com/viewjob?jk=72289279cfc2dcd3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Databricks Developer (Unity Catalog Migration)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DysrupIT</t>
+          <t>U.S. Financial Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -836,69 +836,69 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b253191bad860e34</t>
+          <t>https://www.indeed.com/viewjob?jk=aac712b4e1b735d4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Reliability Engineer</t>
+          <t>Databricks Developer (Unity Catalog Migration)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>DysrupIT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, Tableau, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b0948bec3ed1512</t>
+          <t>https://www.indeed.com/viewjob?jk=b253191bad860e34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Reliability Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bloomerang</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, Tableau, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0fe96b9bdbba45</t>
+          <t>https://www.indeed.com/viewjob?jk=3b0948bec3ed1512</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Application Development and Implementation Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Bloomerang</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0fe96b9bdbba45</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Application Development and Implementation Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eda973817d320c4</t>
+          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9409951346a7ad0d</t>
+          <t>https://www.indeed.com/viewjob?jk=3eda973817d320c4</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af009d50d9ce471a</t>
+          <t>https://www.indeed.com/viewjob?jk=9409951346a7ad0d</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b475180d99aecacf</t>
+          <t>https://www.indeed.com/viewjob?jk=af009d50d9ce471a</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772d08b80e754e75</t>
+          <t>https://www.indeed.com/viewjob?jk=b475180d99aecacf</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3fd193c06ae0581</t>
+          <t>https://www.indeed.com/viewjob?jk=772d08b80e754e75</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b65c34e565b992c</t>
+          <t>https://www.indeed.com/viewjob?jk=e3fd193c06ae0581</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779fe138ded484b</t>
+          <t>https://www.indeed.com/viewjob?jk=2b65c34e565b992c</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb1c755d148975ff</t>
+          <t>https://www.indeed.com/viewjob?jk=0779fe138ded484b</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613cd064c5c54a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=cb1c755d148975ff</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=120779d15d1fcfb6</t>
+          <t>https://www.indeed.com/viewjob?jk=613cd064c5c54a4c</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67914dd58a58a8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=120779d15d1fcfb6</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31d4f4143f7cb28</t>
+          <t>https://www.indeed.com/viewjob?jk=67914dd58a58a8d4</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a5289604bca0cff</t>
+          <t>https://www.indeed.com/viewjob?jk=a31d4f4143f7cb28</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3fe4280a2c93391</t>
+          <t>https://www.indeed.com/viewjob?jk=4a5289604bca0cff</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae284e6548c3258</t>
+          <t>https://www.indeed.com/viewjob?jk=f3fe4280a2c93391</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbe9517a3231d13b</t>
+          <t>https://www.indeed.com/viewjob?jk=cae284e6548c3258</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425185029b9803cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fbe9517a3231d13b</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e4cfd7cccd7103</t>
+          <t>https://www.indeed.com/viewjob?jk=425185029b9803cd</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee699af0925dbbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=05e4cfd7cccd7103</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beebec88652a0ad1</t>
+          <t>https://www.indeed.com/viewjob?jk=ee699af0925dbbc0</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d241129f70a15de3</t>
+          <t>https://www.indeed.com/viewjob?jk=beebec88652a0ad1</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811f9831e5bf2622</t>
+          <t>https://www.indeed.com/viewjob?jk=d241129f70a15de3</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d5324a2b8a1805</t>
+          <t>https://www.indeed.com/viewjob?jk=811f9831e5bf2622</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50f7ae8262615bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=48d5324a2b8a1805</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b295f641478562</t>
+          <t>https://www.indeed.com/viewjob?jk=50f7ae8262615bc7</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c092bdfadcd07b8</t>
+          <t>https://www.indeed.com/viewjob?jk=13b295f641478562</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4028439241ee86b</t>
+          <t>https://www.indeed.com/viewjob?jk=7c092bdfadcd07b8</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7c190952f3113a4</t>
+          <t>https://www.indeed.com/viewjob?jk=e4028439241ee86b</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d90ab183a51383</t>
+          <t>https://www.indeed.com/viewjob?jk=f7c190952f3113a4</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10752c112f86257</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d90ab183a51383</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523d0e5286ecdc4d</t>
+          <t>https://www.indeed.com/viewjob?jk=c10752c112f86257</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40492208ab43d208</t>
+          <t>https://www.indeed.com/viewjob?jk=523d0e5286ecdc4d</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cd193841933bb</t>
+          <t>https://www.indeed.com/viewjob?jk=40492208ab43d208</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MDM Architect</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,59 +2176,59 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c2c9fdda4f8d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cd193841933bb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data and Cloud Engineer</t>
+          <t>MDM Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Zookeeper, YARN</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c2c9fdda4f8d1c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da4ecc01920f955</t>
+          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data and Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f1eb8e2a6e504b</t>
+          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587249eddf698e94</t>
+          <t>https://www.indeed.com/viewjob?jk=1da4ecc01920f955</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Business Systems Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Infoville, Inc</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,99 +2341,99 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d7fde96960560b</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f1eb8e2a6e504b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
+          <t>https://www.indeed.com/viewjob?jk=587249eddf698e94</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Business Systems Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Infoville, Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d7fde96960560b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,29 +2446,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,19 +2491,19 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,94 +2526,94 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>pointer infotech L.L.C</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
+          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
+          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>pointer infotech L.L.C</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
+          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer, Forward Deployed Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,24 +2656,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
+          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>OIC Platform Engineer</t>
+          <t>Oracle Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2696,29 +2696,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
+          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Build-A-Bear Workshop</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
+          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>OIC Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Reno, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
+          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>STORD Warehouse</t>
+          <t>Build-A-Bear Workshop</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Glue, IAM, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b9675535a55f10</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b9675535a55f10</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BrightVine Solutions</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24293ea9e15ad0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Analytics Platform Engineer Alteryx</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BrightVine Solutions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Garland, TX, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
+          <t>https://www.indeed.com/viewjob?jk=24293ea9e15ad0ca</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Streaming Data Engineer</t>
+          <t>Analytics Platform Engineer Alteryx</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Garland, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,59 +2981,59 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
+          <t>https://www.indeed.com/viewjob?jk=d2509a4fb0efe928</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Devops Engineer (remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>Preferred Credit, Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Cloud, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
+          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DevOps Engineer (local)</t>
+          <t>Streaming Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
+          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Real-Time Data Engineer</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Associate - Analytics Engineer</t>
+          <t>Devops Engineer (remote)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
+          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>DevOps Engineer (local)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,24 +3181,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
+          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Real-Time Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
+          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
+          <t>Senior Associate - Analytics Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
+          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Apache Kafka Developer</t>
+          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3361,24 +3361,24 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
+          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MicroStrategy Architect</t>
+          <t>Apache Kafka Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Data Meaning</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
+          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>MicroStrategy Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Data Meaning</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,59 +3471,59 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
+          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
+          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,17 +3531,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
+          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
+          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
+          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
+          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
+          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
+          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Junior Platform Engineer</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Clarity Innovations, LLC</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
+          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect (Remote)</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
+          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Platform Foundation</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
+          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer – Platform Foundation</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Wellvana Health</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
+          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Java Engineer with NetSuite Experience</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>Wellvana Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
+          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>Senior Java Engineer with NetSuite Experience</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
+          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
+          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
+          <t>Associate Developer, IT Applications</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
+          <t>RDS, Azure, Event Hubs, Hadoop, Spark, MongoDB, Jenkins, GitHub Actions, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
+          <t>https://www.indeed.com/viewjob?jk=01f79cbad8ac813d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (API-focused)</t>
+          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Off Duty Management</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Katy, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Specialist, Application Development</t>
+          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,94 +4101,94 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Founding Data Engineer</t>
+          <t>Senior Specialist, Application Development</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Patient Funding Alternatives</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Backend Software Engineer (API-focused)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>Off Duty Management</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Katy, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, ETL, ELT, Git, Python, SQL</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5a20dc79ac25721</t>
+          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Founding Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Patient Funding Alternatives</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, ETL, ELT, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
+          <t>https://www.indeed.com/viewjob?jk=c5a20dc79ac25721</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
+          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>OpenShift Administrator</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
+          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
+          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>OpenShift Administrator</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer II - SRE</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
+          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Database Developer Expert</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
+          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Database Developer Expert</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Merck KGaA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Java Architect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Merck KGaA</t>
+          <t>Softpath System LLC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
+          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
+          <t>https://www.indeed.com/viewjob?jk=fe74c0137bb982fb</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Architect</t>
+          <t>Senior Full Stack Engineer (Payments)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Softpath System LLC</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe74c0137bb982fb</t>
+          <t>https://www.indeed.com/viewjob?jk=096faff176ae84dc</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa01236e58a71dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Payments)</t>
+          <t>.NET Engineer with Dicom</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096faff176ae84dc</t>
+          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Enterprise Knowledge</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
+          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>.NET Engineer with Dicom</t>
+          <t>Ai Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
+          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Asst Dir-DevOps Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Enterprise Knowledge</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,85 +4791,15 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Ai Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Johnson Controls</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Asst Dir-DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Moody's</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4f20f826b053e576</t>
         </is>

--- a/results/job_matches_2026-07-17.xlsx
+++ b/results/job_matches_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,35 +573,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>Hilti Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22.2</v>
+        <v>24.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, clustering keys</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba13c042faeff40f</t>
+          <t>https://www.indeed.com/viewjob?jk=0a8b281e1b138c8f</t>
         </is>
       </c>
     </row>
@@ -643,60 +643,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meso Scale Diagnostics</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21.5</v>
+        <v>22.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, Databricks, BigQuery</t>
+          <t>AWS, S3, RDS, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, clustering keys</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=040188cbf02542cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba13c042faeff40f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Meso Scale Diagnostics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=387fc6b51ae76f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=040188cbf02542cc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -736,19 +736,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12d58810cbcb954b</t>
+          <t>https://www.indeed.com/viewjob?jk=387fc6b51ae76f3d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AWS Platform Specialist</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30dc1ebf3576193b</t>
+          <t>https://www.indeed.com/viewjob?jk=12d58810cbcb954b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer ll</t>
+          <t>AWS Platform Specialist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, SQS, SNS, ECS, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72289279cfc2dcd3</t>
+          <t>https://www.indeed.com/viewjob?jk=30dc1ebf3576193b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Site Reliability Engineer ll</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U.S. Financial Technology</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,29 +836,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, SQS, SNS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aac712b4e1b735d4</t>
+          <t>https://www.indeed.com/viewjob?jk=72289279cfc2dcd3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Databricks Developer (Unity Catalog Migration)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DysrupIT</t>
+          <t>U.S. Financial Technology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -871,69 +871,69 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b253191bad860e34</t>
+          <t>https://www.indeed.com/viewjob?jk=aac712b4e1b735d4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Reliability Engineer</t>
+          <t>Databricks Developer (Unity Catalog Migration)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>DysrupIT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, Tableau, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b0948bec3ed1512</t>
+          <t>https://www.indeed.com/viewjob?jk=b253191bad860e34</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Reliability Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bloomerang</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, Tableau, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0fe96b9bdbba45</t>
+          <t>https://www.indeed.com/viewjob?jk=3b0948bec3ed1512</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Application Development and Implementation Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Bloomerang</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0fe96b9bdbba45</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Application Development and Implementation Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eda973817d320c4</t>
+          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9409951346a7ad0d</t>
+          <t>https://www.indeed.com/viewjob?jk=3eda973817d320c4</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af009d50d9ce471a</t>
+          <t>https://www.indeed.com/viewjob?jk=9409951346a7ad0d</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b475180d99aecacf</t>
+          <t>https://www.indeed.com/viewjob?jk=af009d50d9ce471a</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772d08b80e754e75</t>
+          <t>https://www.indeed.com/viewjob?jk=b475180d99aecacf</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3fd193c06ae0581</t>
+          <t>https://www.indeed.com/viewjob?jk=772d08b80e754e75</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b65c34e565b992c</t>
+          <t>https://www.indeed.com/viewjob?jk=e3fd193c06ae0581</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779fe138ded484b</t>
+          <t>https://www.indeed.com/viewjob?jk=2b65c34e565b992c</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb1c755d148975ff</t>
+          <t>https://www.indeed.com/viewjob?jk=0779fe138ded484b</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613cd064c5c54a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=cb1c755d148975ff</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=120779d15d1fcfb6</t>
+          <t>https://www.indeed.com/viewjob?jk=613cd064c5c54a4c</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67914dd58a58a8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=120779d15d1fcfb6</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31d4f4143f7cb28</t>
+          <t>https://www.indeed.com/viewjob?jk=67914dd58a58a8d4</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a5289604bca0cff</t>
+          <t>https://www.indeed.com/viewjob?jk=a31d4f4143f7cb28</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3fe4280a2c93391</t>
+          <t>https://www.indeed.com/viewjob?jk=4a5289604bca0cff</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae284e6548c3258</t>
+          <t>https://www.indeed.com/viewjob?jk=f3fe4280a2c93391</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbe9517a3231d13b</t>
+          <t>https://www.indeed.com/viewjob?jk=cae284e6548c3258</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425185029b9803cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fbe9517a3231d13b</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e4cfd7cccd7103</t>
+          <t>https://www.indeed.com/viewjob?jk=425185029b9803cd</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee699af0925dbbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=05e4cfd7cccd7103</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beebec88652a0ad1</t>
+          <t>https://www.indeed.com/viewjob?jk=ee699af0925dbbc0</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d241129f70a15de3</t>
+          <t>https://www.indeed.com/viewjob?jk=beebec88652a0ad1</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811f9831e5bf2622</t>
+          <t>https://www.indeed.com/viewjob?jk=d241129f70a15de3</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d5324a2b8a1805</t>
+          <t>https://www.indeed.com/viewjob?jk=811f9831e5bf2622</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50f7ae8262615bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=48d5324a2b8a1805</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b295f641478562</t>
+          <t>https://www.indeed.com/viewjob?jk=50f7ae8262615bc7</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c092bdfadcd07b8</t>
+          <t>https://www.indeed.com/viewjob?jk=13b295f641478562</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4028439241ee86b</t>
+          <t>https://www.indeed.com/viewjob?jk=7c092bdfadcd07b8</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7c190952f3113a4</t>
+          <t>https://www.indeed.com/viewjob?jk=e4028439241ee86b</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d90ab183a51383</t>
+          <t>https://www.indeed.com/viewjob?jk=f7c190952f3113a4</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10752c112f86257</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d90ab183a51383</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523d0e5286ecdc4d</t>
+          <t>https://www.indeed.com/viewjob?jk=c10752c112f86257</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40492208ab43d208</t>
+          <t>https://www.indeed.com/viewjob?jk=523d0e5286ecdc4d</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cd193841933bb</t>
+          <t>https://www.indeed.com/viewjob?jk=40492208ab43d208</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MDM Architect</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c2c9fdda4f8d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cd193841933bb</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
+          <t>Data and Cloud Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
+          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data and Cloud Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Zookeeper, YARN</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
+          <t>https://www.indeed.com/viewjob?jk=1da4ecc01920f955</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da4ecc01920f955</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f1eb8e2a6e504b</t>
         </is>
       </c>
     </row>
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f1eb8e2a6e504b</t>
+          <t>https://www.indeed.com/viewjob?jk=587249eddf698e94</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587249eddf698e94</t>
+          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
         </is>
       </c>
     </row>
@@ -2428,25 +2428,25 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Sr Backend Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,42 +2456,42 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Sr Backend Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
+          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
         </is>
       </c>
     </row>
@@ -2526,19 +2526,19 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,19 +2561,19 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2586,104 +2586,104 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
+          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>pointer infotech L.L.C</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
+          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
+          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
+          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer, Forward Deployed Engineer</t>
+          <t>Data Engineer - Lilly Medicine Foundry</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
+          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>OIC Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>pointer infotech L.L.C</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
+          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Build-A-Bear Workshop</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
+          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Oracle Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
+          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Data Engineer, Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b9675535a55f10</t>
+          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>OIC Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
+          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BrightVine Solutions</t>
+          <t>Build-A-Bear Workshop</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24293ea9e15ad0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Analytics Platform Engineer Alteryx</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Garland, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2509a4fb0efe928</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b9675535a55f10</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Preferred Credit, Inc.</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Saint Cloud, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Streaming Data Engineer</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>BrightVine Solutions</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,94 +3086,94 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
+          <t>https://www.indeed.com/viewjob?jk=24293ea9e15ad0ca</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Analytics Platform Engineer Alteryx</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Garland, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Devops Engineer (remote)</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
+          <t>https://www.indeed.com/viewjob?jk=d2509a4fb0efe928</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DevOps Engineer (local)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>Preferred Credit, Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Saint Cloud, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,24 +3181,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
+          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Real-Time Data Engineer</t>
+          <t>Streaming Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3221,29 +3221,29 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Associate - Analytics Engineer</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
+          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
+          <t>Devops Engineer (remote)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
+          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>DevOps Engineer (local)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,24 +3321,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
+          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Real-Time Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
+          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Apache Kafka Developer</t>
+          <t>Senior Associate - Analytics Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,24 +3391,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3431,24 +3431,24 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MicroStrategy Architect</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Data Meaning</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,137 +3506,137 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
+          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Apache Kafka Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
+          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
+          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>MicroStrategy Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Data Meaning</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
+          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
+          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
+          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
+          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
+          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Platform Foundation</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
+          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Wellvana Health</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
+          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Java Engineer with NetSuite Experience</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
+          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
+          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Associate Developer, IT Applications</t>
+          <t>Senior Software Engineer, Identity Platform</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Prove</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Hadoop, Spark, MongoDB, Jenkins, GitHub Actions, Maven, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01f79cbad8ac813d</t>
+          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
+          <t>Senior Java Engineer with NetSuite Experience</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
+          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
+          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Specialist, Application Development</t>
+          <t>Senior Data Engineer – Platform Foundation</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (API-focused)</t>
+          <t>Associate Developer, IT Applications</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Off Duty Management</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Katy, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,42 +4161,42 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Event Hubs, Hadoop, Spark, MongoDB, Jenkins, GitHub Actions, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=01f79cbad8ac813d</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Founding Data Engineer</t>
+          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Patient Funding Alternatives</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,94 +4206,94 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior Specialist, Application Development</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, ETL, ELT, Git, Python, SQL</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5a20dc79ac25721</t>
+          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
+          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Database Developer Expert</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
+          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>OpenShift Administrator</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Merck KGaA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Founding Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Patient Funding Alternatives</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, ETL, ELT, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
+          <t>https://www.indeed.com/viewjob?jk=c5a20dc79ac25721</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Database Developer Expert</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
+          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Merck KGaA</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
+          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Architect</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Softpath System LLC</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe74c0137bb982fb</t>
+          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Payments)</t>
+          <t>OpenShift Administrator</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096faff176ae84dc</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>.NET Engineer with Dicom</t>
+          <t>Senior Full Stack Java Architect</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Softpath System LLC</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
+          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
+          <t>https://www.indeed.com/viewjob?jk=fe74c0137bb982fb</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Senior Full Stack Engineer (Payments)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Enterprise Knowledge</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
+          <t>https://www.indeed.com/viewjob?jk=096faff176ae84dc</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Ai Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Asst Dir-DevOps Engineer</t>
+          <t>.NET Engineer with Dicom</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,15 +4791,120 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Software Engineer III- Eng</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Sunrise, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Ai Engineer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Johnson Controls</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Asst Dir-DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
           <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4f20f826b053e576</t>
         </is>

--- a/results/job_matches_2026-07-17.xlsx
+++ b/results/job_matches_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
+          <t>AI Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
+          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Business Systems Analyst</t>
+          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Infoville, Inc</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d7fde96960560b</t>
+          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Backend Engineer</t>
+          <t>Senior Business Systems Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>Infoville, Inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d7fde96960560b</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,42 +2491,42 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Sr Backend Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
+          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
         </is>
       </c>
     </row>
@@ -2561,19 +2561,19 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2586,24 +2586,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2626,24 +2626,24 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
+          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer - Lilly Medicine Foundry</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Lilly Medicine Foundry</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>pointer infotech L.L.C</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
+          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>pointer infotech L.L.C</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
+          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
+          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer, Forward Deployed Engineer</t>
+          <t>Oracle Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
+          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>OIC Platform Engineer</t>
+          <t>Data Engineer, Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
+          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>OIC Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Build-A-Bear Workshop</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
+          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2509a4fb0efe928</t>
+          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Preferred Credit, Inc.</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Saint Cloud, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
+          <t>https://www.indeed.com/viewjob?jk=d2509a4fb0efe928</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Streaming Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Preferred Credit, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Cloud, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
+          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Streaming Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
+          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Devops Engineer (remote)</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
+          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DevOps Engineer (local)</t>
+          <t>Devops Engineer (remote)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
+          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Real-Time Data Engineer</t>
+          <t>DevOps Engineer (local)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Associate - Analytics Engineer</t>
+          <t>Real-Time Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
+          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Associate - Analytics Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,24 +3426,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
+          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
+          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Apache Kafka Developer</t>
+          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02731878163cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr. DevOps Engineer - Digital Assets</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0528faeb6919f2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,19 +3611,19 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
+          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>MicroStrategy Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Data Meaning</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
+          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MicroStrategy Architect</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Data Meaning</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,69 +3671,69 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
+          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
+          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
+          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
+          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
+          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
+          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
+          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
+          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Sr. Java/React FSE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=7523ee959e30aea8</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Sr. Java/React FSE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,77 +3986,77 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfa043b9e204f89</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity Platform</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Prove</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
+          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Java Engineer with NetSuite Experience</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
+          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>Senior Software Engineer, Identity Platform</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Prove</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
+          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Platform Foundation</t>
+          <t>Senior Java Engineer with NetSuite Experience</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Associate Developer, IT Applications</t>
+          <t>Sr Salesforce HealthCloud Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>TriWest Healthcare Alliance</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Hadoop, Spark, MongoDB, Jenkins, GitHub Actions, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01f79cbad8ac813d</t>
+          <t>https://www.indeed.com/viewjob?jk=e4ae0d314a98a06b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
+          <t>Senior Data Engineer – Platform Foundation</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
+          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Specialist, Application Development</t>
+          <t>Greenfield Associate Full Stack Developer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
+          <t>Associate Developer, IT Applications</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,147 +4266,147 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
+          <t>RDS, Azure, Event Hubs, Hadoop, Spark, MongoDB, Jenkins, GitHub Actions, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
+          <t>https://www.indeed.com/viewjob?jk=01f79cbad8ac813d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Senior Specialist, Application Development</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
+          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Database Developer Expert</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
+          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Merck KGaA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
+          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Founding Data Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Patient Funding Alternatives</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Database Developer Expert</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, ETL, ELT, Git, Python, SQL</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5a20dc79ac25721</t>
+          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Merck KGaA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>MMOTA Automation &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>OpenShift Administrator</t>
+          <t>Founding Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Patient Funding Alternatives</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, ETL, ELT, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
+          <t>https://www.indeed.com/viewjob?jk=c5a20dc79ac25721</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Architect</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Softpath System LLC</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe74c0137bb982fb</t>
+          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Payments)</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096faff176ae84dc</t>
+          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,19 +4766,19 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
+          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>.NET Engineer with Dicom</t>
+          <t>OpenShift Administrator</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer III- Eng</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Ai Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Asst Dir-DevOps Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,15 +4896,225 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Java Architect</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Softpath System LLC</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Newark, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe74c0137bb982fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>.NET Engineer with Dicom</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Digital Dhara LLC</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Software Engineer III- Eng</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Sunrise, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Ai Engineer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Johnson Controls</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Asst Dir-DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
           <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4f20f826b053e576</t>
         </is>

--- a/results/job_matches_2026-07-17.xlsx
+++ b/results/job_matches_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Nitor Infotech</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.9</v>
+        <v>25</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Google Cloud Platform, BigQuery</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Azure, Blob Storage, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d76ba5e0a95c573</t>
+          <t>https://www.indeed.com/viewjob?jk=9691a4b3c751e344</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Hilti Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25.7</v>
+        <v>24.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9020dafbdc31c1</t>
+          <t>https://www.indeed.com/viewjob?jk=0a8b281e1b138c8f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nitor Infotech</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Azure, Blob Storage, Google Cloud Platform, GCP</t>
+          <t>IAM, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Oozie, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9691a4b3c751e344</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed5e67a7bd26cdb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hilti Group</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24.3</v>
+        <v>22.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, S3, RDS, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, clustering keys</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8b281e1b138c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba13c042faeff40f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Meso Scale Diagnostics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>22.2</v>
+        <v>21.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IAM, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Oozie, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed5e67a7bd26cdb</t>
+          <t>https://www.indeed.com/viewjob?jk=040188cbf02542cc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22.2</v>
+        <v>20.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, clustering keys</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba13c042faeff40f</t>
+          <t>https://www.indeed.com/viewjob?jk=387fc6b51ae76f3d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer ll</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meso Scale Diagnostics</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21.5</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, Databricks, BigQuery</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, SQS, SNS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=040188cbf02542cc</t>
+          <t>https://www.indeed.com/viewjob?jk=72289279cfc2dcd3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>U.S. Financial Technology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,33 +727,33 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=387fc6b51ae76f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=aac712b4e1b735d4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Databricks Developer (Unity Catalog Migration)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>DysrupIT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -762,46 +762,46 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12d58810cbcb954b</t>
+          <t>https://www.indeed.com/viewjob?jk=b253191bad860e34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AWS Platform Specialist</t>
+          <t>Reliability Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, Tableau, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30dc1ebf3576193b</t>
+          <t>https://www.indeed.com/viewjob?jk=3b0948bec3ed1512</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer ll</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>Bloomerang</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, SQS, SNS, ECS, IAM, RDS</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,102 +846,102 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72289279cfc2dcd3</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0fe96b9bdbba45</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Application Development and Implementation Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U.S. Financial Technology</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aac712b4e1b735d4</t>
+          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Databricks Developer (Unity Catalog Migration)</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DysrupIT</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b253191bad860e34</t>
+          <t>https://www.indeed.com/viewjob?jk=9409951346a7ad0d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Reliability Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, Tableau, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b0948bec3ed1512</t>
+          <t>https://www.indeed.com/viewjob?jk=af009d50d9ce471a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bloomerang</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0fe96b9bdbba45</t>
+          <t>https://www.indeed.com/viewjob?jk=b475180d99aecacf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Application Development and Implementation Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
+          <t>https://www.indeed.com/viewjob?jk=772d08b80e754e75</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Sr Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eda973817d320c4</t>
+          <t>https://www.indeed.com/viewjob?jk=e3fd193c06ae0581</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9409951346a7ad0d</t>
+          <t>https://www.indeed.com/viewjob?jk=2b65c34e565b992c</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af009d50d9ce471a</t>
+          <t>https://www.indeed.com/viewjob?jk=0779fe138ded484b</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b475180d99aecacf</t>
+          <t>https://www.indeed.com/viewjob?jk=cb1c755d148975ff</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772d08b80e754e75</t>
+          <t>https://www.indeed.com/viewjob?jk=613cd064c5c54a4c</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3fd193c06ae0581</t>
+          <t>https://www.indeed.com/viewjob?jk=120779d15d1fcfb6</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b65c34e565b992c</t>
+          <t>https://www.indeed.com/viewjob?jk=67914dd58a58a8d4</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779fe138ded484b</t>
+          <t>https://www.indeed.com/viewjob?jk=a31d4f4143f7cb28</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb1c755d148975ff</t>
+          <t>https://www.indeed.com/viewjob?jk=4a5289604bca0cff</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613cd064c5c54a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=f3fe4280a2c93391</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=120779d15d1fcfb6</t>
+          <t>https://www.indeed.com/viewjob?jk=cae284e6548c3258</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67914dd58a58a8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=fbe9517a3231d13b</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31d4f4143f7cb28</t>
+          <t>https://www.indeed.com/viewjob?jk=425185029b9803cd</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a5289604bca0cff</t>
+          <t>https://www.indeed.com/viewjob?jk=05e4cfd7cccd7103</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3fe4280a2c93391</t>
+          <t>https://www.indeed.com/viewjob?jk=ee699af0925dbbc0</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae284e6548c3258</t>
+          <t>https://www.indeed.com/viewjob?jk=beebec88652a0ad1</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbe9517a3231d13b</t>
+          <t>https://www.indeed.com/viewjob?jk=d241129f70a15de3</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425185029b9803cd</t>
+          <t>https://www.indeed.com/viewjob?jk=811f9831e5bf2622</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e4cfd7cccd7103</t>
+          <t>https://www.indeed.com/viewjob?jk=48d5324a2b8a1805</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee699af0925dbbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=50f7ae8262615bc7</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beebec88652a0ad1</t>
+          <t>https://www.indeed.com/viewjob?jk=13b295f641478562</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d241129f70a15de3</t>
+          <t>https://www.indeed.com/viewjob?jk=7c092bdfadcd07b8</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811f9831e5bf2622</t>
+          <t>https://www.indeed.com/viewjob?jk=e4028439241ee86b</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d5324a2b8a1805</t>
+          <t>https://www.indeed.com/viewjob?jk=f7c190952f3113a4</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50f7ae8262615bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d90ab183a51383</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b295f641478562</t>
+          <t>https://www.indeed.com/viewjob?jk=c10752c112f86257</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c092bdfadcd07b8</t>
+          <t>https://www.indeed.com/viewjob?jk=523d0e5286ecdc4d</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4028439241ee86b</t>
+          <t>https://www.indeed.com/viewjob?jk=40492208ab43d208</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,102 +2036,102 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7c190952f3113a4</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cd193841933bb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Data and Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d90ab183a51383</t>
+          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10752c112f86257</t>
+          <t>https://www.indeed.com/viewjob?jk=1da4ecc01920f955</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523d0e5286ecdc4d</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f1eb8e2a6e504b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,59 +2176,59 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40492208ab43d208</t>
+          <t>https://www.indeed.com/viewjob?jk=587249eddf698e94</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>AI Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cd193841933bb</t>
+          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data and Cloud Engineer</t>
+          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Zookeeper, YARN</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
+          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Senior Business Systems Analyst</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Infoville, Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da4ecc01920f955</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d7fde96960560b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Quality Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f1eb8e2a6e504b</t>
+          <t>https://www.indeed.com/viewjob?jk=d99840edec18518b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Backend Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587249eddf698e94</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Forward Deployment Engineer</t>
+          <t>Sr Backend Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
+          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
+          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Business Systems Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Infoville, Inc</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d7fde96960560b</t>
+          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
+          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
+          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
+          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee0e6ad03a3ec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
+          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer - Lilly Medicine Foundry</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
         </is>
       </c>
     </row>
@@ -2783,20 +2783,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>pointer infotech L.L.C</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
+          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
         </is>
       </c>
     </row>
@@ -2818,20 +2818,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Florence, AL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
+          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2862,46 +2862,46 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer, Forward Deployed Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd0df0dccdfb9f2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>OIC Platform Engineer</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2932,73 +2932,73 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b23a0e4bd54aca</t>
+          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
+          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b9675535a55f10</t>
+          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Data Engineer - Lilly Medicine Foundry</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
+          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BrightVine Solutions</t>
+          <t>pointer infotech L.L.C</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24293ea9e15ad0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Analytics Platform Engineer Alteryx</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Garland, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
+          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Oracle Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
+          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Data Engineer, Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2509a4fb0efe928</t>
+          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Preferred Credit, Inc.</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Saint Cloud, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,14 +3226,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Streaming Data Engineer</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3247,11 +3247,11 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,199 +3261,199 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b9675535a55f10</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Devops Engineer (remote)</t>
+          <t>Analytics Platform Engineer Alteryx</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Garland, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DevOps Engineer (local)</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pitch Aeronautics</t>
+          <t>BrightVine Solutions</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
+          <t>https://www.indeed.com/viewjob?jk=24293ea9e15ad0ca</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Real-Time Data Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e8597c74939cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Associate - Analytics Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
+          <t>https://www.indeed.com/viewjob?jk=d2509a4fb0efe928</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Preferred Credit, Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Cloud, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
+          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
+          <t>Streaming Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
+          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer - Digital Assets</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0528faeb6919f2</t>
+          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Devops Engineer (remote)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
+          <t>https://www.indeed.com/viewjob?jk=8d06989f63f80692</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MicroStrategy Architect</t>
+          <t>DevOps Engineer (local)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Data Meaning</t>
+          <t>Pitch Aeronautics</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44493866380de3d</t>
+          <t>https://www.indeed.com/viewjob?jk=05962395e65b1886</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Senior Associate - Analytics Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
+          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Sr. DevOps Engineer - Digital Assets</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,42 +3706,42 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d42e314159c908</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0528faeb6919f2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,129 +3786,129 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
+          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
+          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
+          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
+          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr. Java/React FSE</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7523ee959e30aea8</t>
+          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Java/React FSE</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfa043b9e204f89</t>
+          <t>https://www.indeed.com/viewjob?jk=85a5a7b7163788ca</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=100f0edfd16804d0</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,102 +4066,102 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
+          <t>https://www.indeed.com/viewjob?jk=6c73fdab7d4125b5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity Platform</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Prove</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
+          <t>https://www.indeed.com/viewjob?jk=589d96f5043796e6</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Java Engineer with NetSuite Experience</t>
+          <t>Sr. Java/React FSE</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
+          <t>https://www.indeed.com/viewjob?jk=7523ee959e30aea8</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr Salesforce HealthCloud Data Engineer</t>
+          <t>Sr. Java/React FSE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TriWest Healthcare Alliance</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,129 +4171,129 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4ae0d314a98a06b</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfa043b9e204f89</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Platform Foundation</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062b0a0b038ae28f</t>
+          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Greenfield Associate Full Stack Developer</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
+          <t>https://www.indeed.com/viewjob?jk=870693935117a1a7</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Associate Developer, IT Applications</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Hadoop, Spark, MongoDB, Jenkins, GitHub Actions, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01f79cbad8ac813d</t>
+          <t>https://www.indeed.com/viewjob?jk=1a69e4ca3aede317</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Specialist, Application Development</t>
+          <t>Senior Software Engineer, Identity Platform</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Prove</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Senior Java Engineer with NetSuite Experience</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Plan A Technologies</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
+          <t>https://www.indeed.com/viewjob?jk=3e906b63eead3804</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
+          <t>Sr Salesforce HealthCloud Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TriWest Healthcare Alliance</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
+          <t>https://www.indeed.com/viewjob?jk=e4ae0d314a98a06b</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior AI/Data Science Engineer – Manufacturing &amp; Operations</t>
+          <t>Greenfield Associate Full Stack Developer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,42 +4406,42 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0006d33139e7b7</t>
+          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Associate Developer, IT Applications</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>RDS, Azure, Event Hubs, Hadoop, Spark, MongoDB, Jenkins, GitHub Actions, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,164 +4451,164 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
+          <t>https://www.indeed.com/viewjob?jk=01f79cbad8ac813d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Database Developer Expert</t>
+          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
+          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Merck KGaA</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
+          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
+          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MMOTA Automation &amp; Analytics Engineer</t>
+          <t>Senior Specialist, Application Development</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=326667fe25b59e3f</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Founding Data Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Patient Funding Alternatives</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Database Developer Expert</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, ETL, ELT, Git, Python, SQL</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5a20dc79ac25721</t>
+          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Merck KGaA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, Spark, Scala, MLOps, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab4243907f18fee</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4947a8fe12af52</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>MMOTA Automation &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>OpenShift Administrator</t>
+          <t>Founding Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Patient Funding Alternatives</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, ETL, ELT, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
+          <t>https://www.indeed.com/viewjob?jk=c5a20dc79ac25721</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
+          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
+          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Architect</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Softpath System LLC</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe74c0137bb982fb</t>
+          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>OpenShift Administrator</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,19 +4976,19 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>.NET Engineer with Dicom</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5c95d18f76d05a</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Engineer III- Eng</t>
+          <t>Senior Consultant, Mobile App Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>Travel + Leisure Co.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Ai Engineer</t>
+          <t>Senior UX Software Engineer 7.26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Asst Dir-DevOps Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,7 +5116,252 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f20f826b053e576</t>
+          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PNC Financial Services Group</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Java Architect</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Softpath System LLC</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Newark, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe74c0137bb982fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>UX Software Engineer 6.2026</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>GRVTY</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>.NET Engineer with Dicom</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Digital Dhara LLC</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Software Engineer III- Eng</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Sunrise, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Ai Engineer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Johnson Controls</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
         </is>
       </c>
     </row>
